--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21256,6 +21256,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="909">
+      <c r="A909" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B909" t="n">
+        <v>342245</v>
+      </c>
+      <c r="C909" t="n">
+        <v>0.912999987602234</v>
+      </c>
+      <c r="D909" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="E909" t="n">
+        <v>0.912999987602234</v>
+      </c>
+      <c r="F909" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="G909" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21279,6 +21279,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="910">
+      <c r="A910" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B910" t="n">
+        <v>490993</v>
+      </c>
+      <c r="C910" t="n">
+        <v>0.921000003814697</v>
+      </c>
+      <c r="D910" t="n">
+        <v>0.878000020980835</v>
+      </c>
+      <c r="E910" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="F910" t="n">
+        <v>0.892499983310699</v>
+      </c>
+      <c r="G910" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21302,6 +21302,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="911">
+      <c r="A911" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B911" t="n">
+        <v>140398</v>
+      </c>
+      <c r="C911" t="n">
+        <v>0.917500019073486</v>
+      </c>
+      <c r="D911" t="n">
+        <v>0.895500004291534</v>
+      </c>
+      <c r="E911" t="n">
+        <v>0.904500007629395</v>
+      </c>
+      <c r="F911" t="n">
+        <v>0.907500028610229</v>
+      </c>
+      <c r="G911" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21325,6 +21325,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="912">
+      <c r="A912" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B912" t="n">
+        <v>350237</v>
+      </c>
+      <c r="C912" t="n">
+        <v>0.94650000333786</v>
+      </c>
+      <c r="D912" t="n">
+        <v>0.915499985218048</v>
+      </c>
+      <c r="E912" t="n">
+        <v>0.919000029563904</v>
+      </c>
+      <c r="F912" t="n">
+        <v>0.934000015258789</v>
+      </c>
+      <c r="G912" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21166,22 +21166,22 @@
     </row>
     <row r="905">
       <c r="A905" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B905" t="n">
-        <v>203378</v>
+        <v>326198</v>
       </c>
       <c r="C905" t="n">
-        <v>0.942499995231628</v>
+        <v>0.950999975204468</v>
       </c>
       <c r="D905" t="n">
-        <v>0.929000020027161</v>
+        <v>0.925999999046326</v>
       </c>
       <c r="E905" t="n">
-        <v>0.940999984741211</v>
+        <v>0.939999997615814</v>
       </c>
       <c r="F905" t="n">
-        <v>0.930000007152557</v>
+        <v>0.945999979972839</v>
       </c>
       <c r="G905" t="s">
         <v>7</v>
@@ -21189,22 +21189,22 @@
     </row>
     <row r="906">
       <c r="A906" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B906" t="n">
-        <v>327429</v>
+        <v>203378</v>
       </c>
       <c r="C906" t="n">
-        <v>0.938000023365021</v>
+        <v>0.942499995231628</v>
       </c>
       <c r="D906" t="n">
-        <v>0.908999979496002</v>
+        <v>0.929000020027161</v>
       </c>
       <c r="E906" t="n">
-        <v>0.9375</v>
+        <v>0.940999984741211</v>
       </c>
       <c r="F906" t="n">
-        <v>0.908999979496002</v>
+        <v>0.930000007152557</v>
       </c>
       <c r="G906" t="s">
         <v>7</v>
@@ -21212,22 +21212,22 @@
     </row>
     <row r="907">
       <c r="A907" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B907" t="n">
-        <v>268880</v>
+        <v>327429</v>
       </c>
       <c r="C907" t="n">
-        <v>0.939000010490417</v>
+        <v>0.938000023365021</v>
       </c>
       <c r="D907" t="n">
-        <v>0.90200001001358</v>
+        <v>0.908999979496002</v>
       </c>
       <c r="E907" t="n">
-        <v>0.90200001001358</v>
+        <v>0.9375</v>
       </c>
       <c r="F907" t="n">
-        <v>0.902499973773956</v>
+        <v>0.908999979496002</v>
       </c>
       <c r="G907" t="s">
         <v>7</v>
@@ -21235,22 +21235,22 @@
     </row>
     <row r="908">
       <c r="A908" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B908" t="n">
-        <v>250869</v>
+        <v>268880</v>
       </c>
       <c r="C908" t="n">
-        <v>0.917999982833862</v>
+        <v>0.939000010490417</v>
       </c>
       <c r="D908" t="n">
-        <v>0.899999976158142</v>
+        <v>0.90200001001358</v>
       </c>
       <c r="E908" t="n">
-        <v>0.910000026226044</v>
+        <v>0.90200001001358</v>
       </c>
       <c r="F908" t="n">
-        <v>0.902999997138977</v>
+        <v>0.902499973773956</v>
       </c>
       <c r="G908" t="s">
         <v>7</v>
@@ -21258,22 +21258,22 @@
     </row>
     <row r="909">
       <c r="A909" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B909" t="n">
-        <v>342245</v>
+        <v>250869</v>
       </c>
       <c r="C909" t="n">
-        <v>0.912999987602234</v>
+        <v>0.917999982833862</v>
       </c>
       <c r="D909" t="n">
-        <v>0.879999995231628</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="E909" t="n">
-        <v>0.912999987602234</v>
+        <v>0.910000026226044</v>
       </c>
       <c r="F909" t="n">
-        <v>0.879999995231628</v>
+        <v>0.902999997138977</v>
       </c>
       <c r="G909" t="s">
         <v>7</v>
@@ -21281,22 +21281,22 @@
     </row>
     <row r="910">
       <c r="A910" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B910" t="n">
-        <v>490993</v>
+        <v>342245</v>
       </c>
       <c r="C910" t="n">
-        <v>0.921000003814697</v>
+        <v>0.912999987602234</v>
       </c>
       <c r="D910" t="n">
-        <v>0.878000020980835</v>
+        <v>0.879999995231628</v>
       </c>
       <c r="E910" t="n">
+        <v>0.912999987602234</v>
+      </c>
+      <c r="F910" t="n">
         <v>0.879999995231628</v>
-      </c>
-      <c r="F910" t="n">
-        <v>0.892499983310699</v>
       </c>
       <c r="G910" t="s">
         <v>7</v>
@@ -21304,22 +21304,22 @@
     </row>
     <row r="911">
       <c r="A911" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B911" t="n">
-        <v>140398</v>
+        <v>490993</v>
       </c>
       <c r="C911" t="n">
-        <v>0.917500019073486</v>
+        <v>0.921000003814697</v>
       </c>
       <c r="D911" t="n">
-        <v>0.895500004291534</v>
+        <v>0.878000020980835</v>
       </c>
       <c r="E911" t="n">
-        <v>0.904500007629395</v>
+        <v>0.879999995231628</v>
       </c>
       <c r="F911" t="n">
-        <v>0.907500028610229</v>
+        <v>0.892499983310699</v>
       </c>
       <c r="G911" t="s">
         <v>7</v>
@@ -21327,24 +21327,47 @@
     </row>
     <row r="912">
       <c r="A912" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B912" t="n">
-        <v>350237</v>
+        <v>140398</v>
       </c>
       <c r="C912" t="n">
-        <v>0.94650000333786</v>
+        <v>0.917500019073486</v>
       </c>
       <c r="D912" t="n">
-        <v>0.915499985218048</v>
+        <v>0.895500004291534</v>
       </c>
       <c r="E912" t="n">
-        <v>0.919000029563904</v>
+        <v>0.904500007629395</v>
       </c>
       <c r="F912" t="n">
-        <v>0.934000015258789</v>
+        <v>0.907500028610229</v>
       </c>
       <c r="G912" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B913" t="n">
+        <v>403803</v>
+      </c>
+      <c r="C913" t="n">
+        <v>0.947000026702881</v>
+      </c>
+      <c r="D913" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E913" t="n">
+        <v>0.947000026702881</v>
+      </c>
+      <c r="F913" t="n">
+        <v>0.893999993801117</v>
+      </c>
+      <c r="G913" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -24165,6 +24165,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="916">
+      <c r="A916" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B916" t="n">
+        <v>373665</v>
+      </c>
+      <c r="C916" t="n">
+        <v>0.986999988555908</v>
+      </c>
+      <c r="D916" t="n">
+        <v>0.945999979972839</v>
+      </c>
+      <c r="E916" t="n">
+        <v>0.977999985218048</v>
+      </c>
+      <c r="F916" t="n">
+        <v>0.964999973773956</v>
+      </c>
+      <c r="G916" t="n">
+        <v>0.964999973773956</v>
+      </c>
+      <c r="H916" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -24191,6 +24191,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="917">
+      <c r="A917" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B917" t="n">
+        <v>263246</v>
+      </c>
+      <c r="C917" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="D917" t="n">
+        <v>0.931999981403351</v>
+      </c>
+      <c r="E917" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="F917" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G917" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="H917" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -733,7 +733,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>5.07641315460205</v>
+        <v>5.07641363143921</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G24" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>5.02760219573975</v>
+        <v>5.02760171890259</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.68592071533203</v>
+        <v>4.68592023849487</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89092969894409</v>
+        <v>4.89092922210693</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49555492401123</v>
+        <v>4.49555444717407</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>4.73473167419434</v>
+        <v>4.73473215103149</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G39" t="n">
-        <v>4.69568204879761</v>
+        <v>4.69568252563477</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>4.68592071533203</v>
+        <v>4.68592023849487</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G43" t="n">
-        <v>4.87140417098999</v>
+        <v>4.87140464782715</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G48" t="n">
-        <v>4.86749982833862</v>
+        <v>4.86749935150146</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>5.02760219573975</v>
+        <v>5.02760171890259</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>5.14474964141846</v>
+        <v>5.14475011825562</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>5.8378758430481</v>
+        <v>5.83787536621094</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>5.78906345367432</v>
+        <v>5.78906393051147</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>5.78906345367432</v>
+        <v>5.78906393051147</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.875</v>
       </c>
       <c r="G72" t="n">
-        <v>5.73537063598633</v>
+        <v>5.73537111282349</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>5.8378758430481</v>
+        <v>5.83787536621094</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81346940994263</v>
+        <v>5.81346988677979</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G80" t="n">
-        <v>5.95014190673828</v>
+        <v>5.95014238357544</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>6.42361545562744</v>
+        <v>6.4236159324646</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.25765609741211</v>
+        <v>6.25765562057495</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>6.32599258422852</v>
+        <v>6.32599210739136</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>6.35039806365967</v>
+        <v>6.35039854049683</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.35039806365967</v>
+        <v>6.35039854049683</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G99" t="n">
-        <v>6.41385316848755</v>
+        <v>6.41385364532471</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>6.27718019485474</v>
+        <v>6.27718067169189</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>6.14050769805908</v>
+        <v>6.14050817489624</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>6.00383520126343</v>
+        <v>6.00383567810059</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>4.85578441619873</v>
+        <v>4.85578489303589</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G117" t="n">
-        <v>4.66834783554077</v>
+        <v>4.66834831237793</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G119" t="n">
-        <v>4.86749982833862</v>
+        <v>4.86749935150146</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G125" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>5.07641315460205</v>
+        <v>5.07641363143921</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.94462203979492</v>
+        <v>4.94462251663208</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G147" t="n">
-        <v>4.63906097412109</v>
+        <v>4.63906049728394</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G156" t="n">
-        <v>4.19780349731445</v>
+        <v>4.19780397415161</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>3.98303198814392</v>
+        <v>3.9830322265625</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G159" t="n">
-        <v>3.94203019142151</v>
+        <v>3.94203042984009</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G162" t="n">
-        <v>3.95569753646851</v>
+        <v>3.95569777488708</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G164" t="n">
-        <v>3.98693752288818</v>
+        <v>3.98693704605103</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.81707239151001</v>
+        <v>3.81707262992859</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G168" t="n">
-        <v>3.7975480556488</v>
+        <v>3.79754781723022</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73702120780945</v>
+        <v>3.73702144622803</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G171" t="n">
-        <v>3.81902503967285</v>
+        <v>3.81902480125427</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G172" t="n">
-        <v>3.69211459159851</v>
+        <v>3.69211483001709</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32505083084106</v>
+        <v>3.32505059242249</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>3.34262299537659</v>
+        <v>3.34262323379517</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.13761401176453</v>
+        <v>3.13761425018311</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G187" t="n">
-        <v>3.18837833404541</v>
+        <v>3.18837809562683</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G189" t="n">
-        <v>3.25280952453613</v>
+        <v>3.25280976295471</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G194" t="n">
-        <v>3.24304747581482</v>
+        <v>3.24304723739624</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>3.68039965629578</v>
+        <v>3.68039989471436</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G199" t="n">
-        <v>3.56520438194275</v>
+        <v>3.56520414352417</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59253907203674</v>
+        <v>3.59253883361816</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.59253907203674</v>
+        <v>3.59253883361816</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G205" t="n">
-        <v>3.5222499370575</v>
+        <v>3.52225017547607</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G208" t="n">
-        <v>3.50858283042908</v>
+        <v>3.50858306884766</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>3.21571278572083</v>
+        <v>3.21571254730225</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10442209243774</v>
+        <v>3.10442233085632</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13175654411316</v>
+        <v>3.13175678253174</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G219" t="n">
-        <v>3.4343888759613</v>
+        <v>3.43438911437988</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>3.62182593345642</v>
+        <v>3.62182569503784</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73702120780945</v>
+        <v>3.73702144622803</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G224" t="n">
-        <v>3.81316733360291</v>
+        <v>3.81316757202148</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G227" t="n">
-        <v>3.82878708839417</v>
+        <v>3.82878732681274</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G234" t="n">
-        <v>3.42853164672852</v>
+        <v>3.42853188514709</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G236" t="n">
-        <v>3.4343888759613</v>
+        <v>3.43438911437988</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G237" t="n">
-        <v>3.46367597579956</v>
+        <v>3.46367621421814</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G238" t="n">
-        <v>3.26647663116455</v>
+        <v>3.26647686958313</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.18252086639404</v>
+        <v>3.18252062797546</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28404927253723</v>
+        <v>3.28404903411865</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G256" t="n">
-        <v>3.29381132125854</v>
+        <v>3.29381155967712</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G259" t="n">
-        <v>3.26647663116455</v>
+        <v>3.26647686958313</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>3.25671458244324</v>
+        <v>3.25671434402466</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>3.24304747581482</v>
+        <v>3.24304723739624</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G270" t="n">
-        <v>3.37971997261047</v>
+        <v>3.37971973419189</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33286070823669</v>
+        <v>3.33286094665527</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G272" t="n">
-        <v>3.17666339874268</v>
+        <v>3.1766631603241</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G275" t="n">
-        <v>3.21571278572083</v>
+        <v>3.21571254730225</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G281" t="n">
-        <v>3.52420258522034</v>
+        <v>3.52420234680176</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.75</v>
       </c>
       <c r="G284" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.75</v>
       </c>
       <c r="G288" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.75</v>
       </c>
       <c r="G290" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G292" t="n">
-        <v>4.14703989028931</v>
+        <v>4.14703941345215</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G294" t="n">
-        <v>3.93422055244446</v>
+        <v>3.93422079086304</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G295" t="n">
-        <v>3.92055296897888</v>
+        <v>3.92055320739746</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>3.76435589790344</v>
+        <v>3.76435565948486</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G303" t="n">
-        <v>3.53201222419739</v>
+        <v>3.53201246261597</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>3.50272536277771</v>
+        <v>3.50272560119629</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>3.62182593345642</v>
+        <v>3.62182569503784</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G306" t="n">
-        <v>3.99279451370239</v>
+        <v>3.99279475212097</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G313" t="n">
-        <v>3.96350765228271</v>
+        <v>3.96350741386414</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G317" t="n">
-        <v>4.15680122375488</v>
+        <v>4.15680170059204</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G320" t="n">
-        <v>4.45357608795166</v>
+        <v>4.45357656478882</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -24214,6 +24214,32 @@
         <v>0.959999978542328</v>
       </c>
       <c r="H917" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B918" t="n">
+        <v>279951</v>
+      </c>
+      <c r="C918" t="n">
+        <v>0.954999983310699</v>
+      </c>
+      <c r="D918" t="n">
+        <v>0.924000024795532</v>
+      </c>
+      <c r="E918" t="n">
+        <v>0.94650000333786</v>
+      </c>
+      <c r="F918" t="n">
+        <v>0.924000024795532</v>
+      </c>
+      <c r="G918" t="n">
+        <v>0.924000024795532</v>
+      </c>
+      <c r="H918" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -733,7 +733,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G24" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89092922210693</v>
+        <v>4.89092969894409</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49555444717407</v>
+        <v>4.49555492401123</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>4.73473215103149</v>
+        <v>4.73473167419434</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G39" t="n">
-        <v>4.69568252563477</v>
+        <v>4.69568204879761</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G43" t="n">
-        <v>4.87140464782715</v>
+        <v>4.87140417098999</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G48" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>5.14475011825562</v>
+        <v>5.14474964141846</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.875</v>
       </c>
       <c r="G72" t="n">
-        <v>5.73537111282349</v>
+        <v>5.73537063598633</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81346988677979</v>
+        <v>5.81346940994263</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G80" t="n">
-        <v>5.95014238357544</v>
+        <v>5.95014190673828</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>6.4236159324646</v>
+        <v>6.42361545562744</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.25765562057495</v>
+        <v>6.25765609741211</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>6.32599210739136</v>
+        <v>6.32599258422852</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G99" t="n">
-        <v>6.41385364532471</v>
+        <v>6.41385316848755</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>6.27718067169189</v>
+        <v>6.27718019485474</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>6.14050817489624</v>
+        <v>6.14050769805908</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>6.00383567810059</v>
+        <v>6.00383520126343</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>4.85578489303589</v>
+        <v>4.85578441619873</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G117" t="n">
-        <v>4.66834831237793</v>
+        <v>4.66834783554077</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G119" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G125" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.94462251663208</v>
+        <v>4.94462203979492</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G147" t="n">
-        <v>4.63906049728394</v>
+        <v>4.63906097412109</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G156" t="n">
-        <v>4.19780397415161</v>
+        <v>4.19780349731445</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>3.9830322265625</v>
+        <v>3.98303198814392</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G159" t="n">
-        <v>3.94203042984009</v>
+        <v>3.94203019142151</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G162" t="n">
-        <v>3.95569777488708</v>
+        <v>3.95569753646851</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G164" t="n">
-        <v>3.98693704605103</v>
+        <v>3.98693752288818</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.81707262992859</v>
+        <v>3.81707239151001</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G168" t="n">
-        <v>3.79754781723022</v>
+        <v>3.7975480556488</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G171" t="n">
-        <v>3.81902480125427</v>
+        <v>3.81902503967285</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G172" t="n">
-        <v>3.69211483001709</v>
+        <v>3.69211459159851</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32505059242249</v>
+        <v>3.32505083084106</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>3.34262323379517</v>
+        <v>3.34262299537659</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.13761425018311</v>
+        <v>3.13761401176453</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G187" t="n">
-        <v>3.18837809562683</v>
+        <v>3.18837833404541</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G189" t="n">
-        <v>3.25280976295471</v>
+        <v>3.25280952453613</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G194" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>3.68039989471436</v>
+        <v>3.68039965629578</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G199" t="n">
-        <v>3.56520414352417</v>
+        <v>3.56520438194275</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G205" t="n">
-        <v>3.52225017547607</v>
+        <v>3.5222499370575</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G208" t="n">
-        <v>3.50858306884766</v>
+        <v>3.50858283042908</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10442233085632</v>
+        <v>3.10442209243774</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13175678253174</v>
+        <v>3.13175654411316</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G219" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G224" t="n">
-        <v>3.81316757202148</v>
+        <v>3.81316733360291</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G227" t="n">
-        <v>3.82878732681274</v>
+        <v>3.82878708839417</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G234" t="n">
-        <v>3.42853188514709</v>
+        <v>3.42853164672852</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G236" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G237" t="n">
-        <v>3.46367621421814</v>
+        <v>3.46367597579956</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G238" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.18252062797546</v>
+        <v>3.18252086639404</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28404903411865</v>
+        <v>3.28404927253723</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G256" t="n">
-        <v>3.29381155967712</v>
+        <v>3.29381132125854</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G259" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>3.25671434402466</v>
+        <v>3.25671458244324</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G270" t="n">
-        <v>3.37971973419189</v>
+        <v>3.37971997261047</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33286094665527</v>
+        <v>3.33286070823669</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G272" t="n">
-        <v>3.1766631603241</v>
+        <v>3.17666339874268</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G275" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G281" t="n">
-        <v>3.52420234680176</v>
+        <v>3.52420258522034</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.75</v>
       </c>
       <c r="G284" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.75</v>
       </c>
       <c r="G288" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.75</v>
       </c>
       <c r="G290" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G292" t="n">
-        <v>4.14703941345215</v>
+        <v>4.14703989028931</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G294" t="n">
-        <v>3.93422079086304</v>
+        <v>3.93422055244446</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G295" t="n">
-        <v>3.92055320739746</v>
+        <v>3.92055296897888</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>3.76435565948486</v>
+        <v>3.76435589790344</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G303" t="n">
-        <v>3.53201246261597</v>
+        <v>3.53201222419739</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>3.50272560119629</v>
+        <v>3.50272536277771</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G306" t="n">
-        <v>3.99279475212097</v>
+        <v>3.99279451370239</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G313" t="n">
-        <v>3.96350741386414</v>
+        <v>3.96350765228271</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G317" t="n">
-        <v>4.15680170059204</v>
+        <v>4.15680122375488</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G320" t="n">
-        <v>4.45357656478882</v>
+        <v>4.45357608795166</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -24240,6 +24240,32 @@
         <v>0.924000024795532</v>
       </c>
       <c r="H918" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B919" t="n">
+        <v>127255</v>
+      </c>
+      <c r="C919" t="n">
+        <v>0.935999989509583</v>
+      </c>
+      <c r="D919" t="n">
+        <v>0.912999987602234</v>
+      </c>
+      <c r="E919" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F919" t="n">
+        <v>0.926500022411346</v>
+      </c>
+      <c r="G919" t="n">
+        <v>0.926500022411346</v>
+      </c>
+      <c r="H919" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -733,7 +733,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>5.07641315460205</v>
+        <v>5.07641363143921</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G24" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>5.02760219573975</v>
+        <v>5.02760171890259</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.68592071533203</v>
+        <v>4.68592023849487</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89092969894409</v>
+        <v>4.89092922210693</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49555492401123</v>
+        <v>4.49555444717407</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>4.73473167419434</v>
+        <v>4.73473215103149</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G39" t="n">
-        <v>4.69568204879761</v>
+        <v>4.69568252563477</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>4.68592071533203</v>
+        <v>4.68592023849487</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G43" t="n">
-        <v>4.87140417098999</v>
+        <v>4.87140464782715</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G48" t="n">
-        <v>4.86749982833862</v>
+        <v>4.86749935150146</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>5.02760219573975</v>
+        <v>5.02760171890259</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>5.14474964141846</v>
+        <v>5.14475011825562</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>5.8378758430481</v>
+        <v>5.83787536621094</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>5.78906345367432</v>
+        <v>5.78906393051147</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>5.78906345367432</v>
+        <v>5.78906393051147</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.875</v>
       </c>
       <c r="G72" t="n">
-        <v>5.73537063598633</v>
+        <v>5.73537111282349</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>5.8378758430481</v>
+        <v>5.83787536621094</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81346940994263</v>
+        <v>5.81346988677979</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G80" t="n">
-        <v>5.95014190673828</v>
+        <v>5.95014238357544</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>6.42361545562744</v>
+        <v>6.4236159324646</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.25765609741211</v>
+        <v>6.25765562057495</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>6.32599258422852</v>
+        <v>6.32599210739136</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>6.35039806365967</v>
+        <v>6.35039854049683</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.35039806365967</v>
+        <v>6.35039854049683</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G99" t="n">
-        <v>6.41385316848755</v>
+        <v>6.41385364532471</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>6.27718019485474</v>
+        <v>6.27718067169189</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>6.14050769805908</v>
+        <v>6.14050817489624</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>6.00383520126343</v>
+        <v>6.00383567810059</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>4.85578441619873</v>
+        <v>4.85578489303589</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G117" t="n">
-        <v>4.66834783554077</v>
+        <v>4.66834831237793</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G119" t="n">
-        <v>4.86749982833862</v>
+        <v>4.86749935150146</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G125" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>5.07641315460205</v>
+        <v>5.07641363143921</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.94462203979492</v>
+        <v>4.94462251663208</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G147" t="n">
-        <v>4.63906097412109</v>
+        <v>4.63906049728394</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G156" t="n">
-        <v>4.19780349731445</v>
+        <v>4.19780397415161</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>3.98303198814392</v>
+        <v>3.9830322265625</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G159" t="n">
-        <v>3.94203019142151</v>
+        <v>3.94203042984009</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G162" t="n">
-        <v>3.95569753646851</v>
+        <v>3.95569777488708</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G164" t="n">
-        <v>3.98693752288818</v>
+        <v>3.98693704605103</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.81707239151001</v>
+        <v>3.81707262992859</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G168" t="n">
-        <v>3.7975480556488</v>
+        <v>3.79754781723022</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73702120780945</v>
+        <v>3.73702144622803</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G171" t="n">
-        <v>3.81902503967285</v>
+        <v>3.81902480125427</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G172" t="n">
-        <v>3.69211459159851</v>
+        <v>3.69211483001709</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32505083084106</v>
+        <v>3.32505059242249</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>3.34262299537659</v>
+        <v>3.34262323379517</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.13761401176453</v>
+        <v>3.13761425018311</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G187" t="n">
-        <v>3.18837833404541</v>
+        <v>3.18837809562683</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G189" t="n">
-        <v>3.25280952453613</v>
+        <v>3.25280976295471</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G194" t="n">
-        <v>3.24304747581482</v>
+        <v>3.24304723739624</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>3.68039965629578</v>
+        <v>3.68039989471436</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G199" t="n">
-        <v>3.56520438194275</v>
+        <v>3.56520414352417</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59253907203674</v>
+        <v>3.59253883361816</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.59253907203674</v>
+        <v>3.59253883361816</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G205" t="n">
-        <v>3.5222499370575</v>
+        <v>3.52225017547607</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G208" t="n">
-        <v>3.50858283042908</v>
+        <v>3.50858306884766</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>3.21571278572083</v>
+        <v>3.21571254730225</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10442209243774</v>
+        <v>3.10442233085632</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13175654411316</v>
+        <v>3.13175678253174</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G219" t="n">
-        <v>3.4343888759613</v>
+        <v>3.43438911437988</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>3.62182593345642</v>
+        <v>3.62182569503784</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73702120780945</v>
+        <v>3.73702144622803</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G224" t="n">
-        <v>3.81316733360291</v>
+        <v>3.81316757202148</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G227" t="n">
-        <v>3.82878708839417</v>
+        <v>3.82878732681274</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G234" t="n">
-        <v>3.42853164672852</v>
+        <v>3.42853188514709</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G236" t="n">
-        <v>3.4343888759613</v>
+        <v>3.43438911437988</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G237" t="n">
-        <v>3.46367597579956</v>
+        <v>3.46367621421814</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G238" t="n">
-        <v>3.26647663116455</v>
+        <v>3.26647686958313</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.18252086639404</v>
+        <v>3.18252062797546</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28404927253723</v>
+        <v>3.28404903411865</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G256" t="n">
-        <v>3.29381132125854</v>
+        <v>3.29381155967712</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G259" t="n">
-        <v>3.26647663116455</v>
+        <v>3.26647686958313</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>3.25671458244324</v>
+        <v>3.25671434402466</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>3.24304747581482</v>
+        <v>3.24304723739624</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G270" t="n">
-        <v>3.37971997261047</v>
+        <v>3.37971973419189</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33286070823669</v>
+        <v>3.33286094665527</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G272" t="n">
-        <v>3.17666339874268</v>
+        <v>3.1766631603241</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G275" t="n">
-        <v>3.21571278572083</v>
+        <v>3.21571254730225</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G281" t="n">
-        <v>3.52420258522034</v>
+        <v>3.52420234680176</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.75</v>
       </c>
       <c r="G284" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.75</v>
       </c>
       <c r="G288" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.75</v>
       </c>
       <c r="G290" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G292" t="n">
-        <v>4.14703989028931</v>
+        <v>4.14703941345215</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G294" t="n">
-        <v>3.93422055244446</v>
+        <v>3.93422079086304</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G295" t="n">
-        <v>3.92055296897888</v>
+        <v>3.92055320739746</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>3.76435589790344</v>
+        <v>3.76435565948486</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G303" t="n">
-        <v>3.53201222419739</v>
+        <v>3.53201246261597</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>3.50272536277771</v>
+        <v>3.50272560119629</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>3.62182593345642</v>
+        <v>3.62182569503784</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G306" t="n">
-        <v>3.99279451370239</v>
+        <v>3.99279475212097</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G313" t="n">
-        <v>3.96350765228271</v>
+        <v>3.96350741386414</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G317" t="n">
-        <v>4.15680122375488</v>
+        <v>4.15680170059204</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G320" t="n">
-        <v>4.45357608795166</v>
+        <v>4.45357656478882</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -24318,6 +24318,32 @@
         <v>0.97299998998642</v>
       </c>
       <c r="H921" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B922" t="n">
+        <v>176773</v>
+      </c>
+      <c r="C922" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="D922" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="E922" t="n">
+        <v>0.959500014781952</v>
+      </c>
+      <c r="F922" t="n">
+        <v>0.948499977588654</v>
+      </c>
+      <c r="G922" t="n">
+        <v>0.948499977588654</v>
+      </c>
+      <c r="H922" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21640,8 +21640,31 @@
       <c r="E925" t="n">
         <v>0.931999981403351</v>
       </c>
-      <c r="F925"/>
+      <c r="F925" t="n">
+        <v>0.920000016689301</v>
+      </c>
       <c r="G925" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B926" t="n">
+        <v>547952</v>
+      </c>
+      <c r="C926" t="n">
+        <v>0.960500001907349</v>
+      </c>
+      <c r="D926" t="n">
+        <v>0.912000000476837</v>
+      </c>
+      <c r="E926" t="n">
+        <v>0.922500014305115</v>
+      </c>
+      <c r="F926"/>
+      <c r="G926" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21663,8 +21663,31 @@
       <c r="E926" t="n">
         <v>0.922500014305115</v>
       </c>
-      <c r="F926"/>
+      <c r="F926" t="n">
+        <v>0.95550000667572</v>
+      </c>
       <c r="G926" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B927" t="n">
+        <v>165049</v>
+      </c>
+      <c r="C927" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D927" t="n">
+        <v>0.924499988555908</v>
+      </c>
+      <c r="E927" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F927"/>
+      <c r="G927" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21686,8 +21686,31 @@
       <c r="E927" t="n">
         <v>0.949999988079071</v>
       </c>
-      <c r="F927"/>
+      <c r="F927" t="n">
+        <v>0.924499988555908</v>
+      </c>
       <c r="G927" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B928" t="n">
+        <v>219102</v>
+      </c>
+      <c r="C928" t="n">
+        <v>0.924000024795532</v>
+      </c>
+      <c r="D928" t="n">
+        <v>0.90200001001358</v>
+      </c>
+      <c r="E928" t="n">
+        <v>0.922999978065491</v>
+      </c>
+      <c r="F928"/>
+      <c r="G928" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21709,8 +21709,31 @@
       <c r="E928" t="n">
         <v>0.922999978065491</v>
       </c>
-      <c r="F928"/>
+      <c r="F928" t="n">
+        <v>0.902499973773956</v>
+      </c>
       <c r="G928" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B929" t="n">
+        <v>441477</v>
+      </c>
+      <c r="C929" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="D929" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="E929" t="n">
+        <v>0.915499985218048</v>
+      </c>
+      <c r="F929"/>
+      <c r="G929" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -21739,6 +21739,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="930">
+      <c r="A930" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B930" t="n">
+        <v>164796</v>
+      </c>
+      <c r="C930" t="n">
+        <v>0.922500014305115</v>
+      </c>
+      <c r="D930" t="n">
+        <v>0.902999997138977</v>
+      </c>
+      <c r="E930" t="n">
+        <v>0.912999987602234</v>
+      </c>
+      <c r="F930" t="n">
+        <v>0.902999997138977</v>
+      </c>
+      <c r="G930" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -24586,13 +24586,13 @@
         <v>46309.2916666667</v>
       </c>
       <c r="B932" t="n">
-        <v>396270</v>
+        <v>398898</v>
       </c>
       <c r="C932" t="n">
         <v>0.939999997615814</v>
       </c>
       <c r="D932" t="n">
-        <v>0.902999997138977</v>
+        <v>0.900499999523163</v>
       </c>
       <c r="E932" t="n">
         <v>0.920499980449677</v>
@@ -24604,6 +24604,32 @@
         <v>0.900499999523163</v>
       </c>
       <c r="H932" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B933" t="n">
+        <v>406635</v>
+      </c>
+      <c r="C933" t="n">
+        <v>0.921999990940094</v>
+      </c>
+      <c r="D933" t="n">
+        <v>0.885999977588654</v>
+      </c>
+      <c r="E933" t="n">
+        <v>0.900499999523163</v>
+      </c>
+      <c r="F933" t="n">
+        <v>0.912000000476837</v>
+      </c>
+      <c r="G933" t="n">
+        <v>0.912000000476837</v>
+      </c>
+      <c r="H933" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -733,7 +733,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G24" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89092922210693</v>
+        <v>4.89092969894409</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49555444717407</v>
+        <v>4.49555492401123</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>4.73473215103149</v>
+        <v>4.73473167419434</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G39" t="n">
-        <v>4.69568252563477</v>
+        <v>4.69568204879761</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G43" t="n">
-        <v>4.87140464782715</v>
+        <v>4.87140417098999</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G48" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>5.14475011825562</v>
+        <v>5.14474964141846</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.875</v>
       </c>
       <c r="G72" t="n">
-        <v>5.73537111282349</v>
+        <v>5.73537063598633</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81346988677979</v>
+        <v>5.81346940994263</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G80" t="n">
-        <v>5.95014238357544</v>
+        <v>5.95014190673828</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>6.4236159324646</v>
+        <v>6.42361545562744</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.25765562057495</v>
+        <v>6.25765609741211</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>6.32599210739136</v>
+        <v>6.32599258422852</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G99" t="n">
-        <v>6.41385364532471</v>
+        <v>6.41385316848755</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>6.27718067169189</v>
+        <v>6.27718019485474</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>6.14050817489624</v>
+        <v>6.14050769805908</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>6.00383567810059</v>
+        <v>6.00383520126343</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>4.85578489303589</v>
+        <v>4.85578441619873</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G117" t="n">
-        <v>4.66834831237793</v>
+        <v>4.66834783554077</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G119" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G125" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.94462251663208</v>
+        <v>4.94462203979492</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G147" t="n">
-        <v>4.63906049728394</v>
+        <v>4.63906097412109</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G156" t="n">
-        <v>4.19780397415161</v>
+        <v>4.19780349731445</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>3.9830322265625</v>
+        <v>3.98303198814392</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G159" t="n">
-        <v>3.94203042984009</v>
+        <v>3.94203019142151</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G162" t="n">
-        <v>3.95569777488708</v>
+        <v>3.95569753646851</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G164" t="n">
-        <v>3.98693704605103</v>
+        <v>3.98693752288818</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.81707262992859</v>
+        <v>3.81707239151001</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G168" t="n">
-        <v>3.79754781723022</v>
+        <v>3.7975480556488</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G171" t="n">
-        <v>3.81902480125427</v>
+        <v>3.81902503967285</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G172" t="n">
-        <v>3.69211483001709</v>
+        <v>3.69211459159851</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32505059242249</v>
+        <v>3.32505083084106</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>3.34262323379517</v>
+        <v>3.34262299537659</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.13761425018311</v>
+        <v>3.13761401176453</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G187" t="n">
-        <v>3.18837809562683</v>
+        <v>3.18837833404541</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G189" t="n">
-        <v>3.25280976295471</v>
+        <v>3.25280952453613</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G194" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>3.68039989471436</v>
+        <v>3.68039965629578</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G199" t="n">
-        <v>3.56520414352417</v>
+        <v>3.56520438194275</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G205" t="n">
-        <v>3.52225017547607</v>
+        <v>3.5222499370575</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G208" t="n">
-        <v>3.50858306884766</v>
+        <v>3.50858283042908</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10442233085632</v>
+        <v>3.10442209243774</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13175678253174</v>
+        <v>3.13175654411316</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G219" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G224" t="n">
-        <v>3.81316757202148</v>
+        <v>3.81316733360291</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G227" t="n">
-        <v>3.82878732681274</v>
+        <v>3.82878708839417</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G234" t="n">
-        <v>3.42853188514709</v>
+        <v>3.42853164672852</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G236" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G237" t="n">
-        <v>3.46367621421814</v>
+        <v>3.46367597579956</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G238" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.18252062797546</v>
+        <v>3.18252086639404</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28404903411865</v>
+        <v>3.28404927253723</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G256" t="n">
-        <v>3.29381155967712</v>
+        <v>3.29381132125854</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G259" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>3.25671434402466</v>
+        <v>3.25671458244324</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G270" t="n">
-        <v>3.37971973419189</v>
+        <v>3.37971997261047</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33286094665527</v>
+        <v>3.33286070823669</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G272" t="n">
-        <v>3.1766631603241</v>
+        <v>3.17666339874268</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G275" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G281" t="n">
-        <v>3.52420234680176</v>
+        <v>3.52420258522034</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.75</v>
       </c>
       <c r="G284" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.75</v>
       </c>
       <c r="G288" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.75</v>
       </c>
       <c r="G290" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G292" t="n">
-        <v>4.14703941345215</v>
+        <v>4.14703989028931</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G294" t="n">
-        <v>3.93422079086304</v>
+        <v>3.93422055244446</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G295" t="n">
-        <v>3.92055320739746</v>
+        <v>3.92055296897888</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>3.76435565948486</v>
+        <v>3.76435589790344</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G303" t="n">
-        <v>3.53201246261597</v>
+        <v>3.53201222419739</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>3.50272560119629</v>
+        <v>3.50272536277771</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G306" t="n">
-        <v>3.99279475212097</v>
+        <v>3.99279451370239</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G313" t="n">
-        <v>3.96350741386414</v>
+        <v>3.96350765228271</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G317" t="n">
-        <v>4.15680170059204</v>
+        <v>4.15680122375488</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G320" t="n">
-        <v>4.45357656478882</v>
+        <v>4.45357608795166</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -24630,6 +24630,32 @@
         <v>0.912000000476837</v>
       </c>
       <c r="H933" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B934" t="n">
+        <v>235725</v>
+      </c>
+      <c r="C934" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="D934" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E934" t="n">
+        <v>0.91049998998642</v>
+      </c>
+      <c r="F934" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G934" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="H934" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -27493,6 +27493,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="936">
+      <c r="A936" t="s">
+        <v>9</v>
+      </c>
+      <c r="B936" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C936" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D936" t="n">
+        <v>0.894999980926514</v>
+      </c>
+      <c r="E936" t="n">
+        <v>0.853500008583069</v>
+      </c>
+      <c r="F936" t="n">
+        <v>0.887000024318695</v>
+      </c>
+      <c r="G936" t="n">
+        <v>0.887000024318695</v>
+      </c>
+      <c r="H936" t="n">
+        <v>268490</v>
+      </c>
+      <c r="I936" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -27522,6 +27522,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="937">
+      <c r="A937" t="s">
+        <v>9</v>
+      </c>
+      <c r="B937" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C937" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="D937" t="n">
+        <v>0.91049998998642</v>
+      </c>
+      <c r="E937" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="F937" t="n">
+        <v>0.890500009059906</v>
+      </c>
+      <c r="G937" t="n">
+        <v>0.890500009059906</v>
+      </c>
+      <c r="H937" t="n">
+        <v>141073</v>
+      </c>
+      <c r="I937" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -775,7 +775,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H14" t="n">
         <v>670102</v>
@@ -833,7 +833,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H16" t="n">
         <v>231471</v>
@@ -862,7 +862,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H17" t="n">
         <v>158512</v>
@@ -1036,7 +1036,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H23" t="n">
         <v>343982</v>
@@ -1065,7 +1065,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G24" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H24" t="n">
         <v>509862</v>
@@ -1123,7 +1123,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H26" t="n">
         <v>168190</v>
@@ -1181,7 +1181,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H28" t="n">
         <v>215478</v>
@@ -1210,7 +1210,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89092922210693</v>
+        <v>4.89092969894409</v>
       </c>
       <c r="H29" t="n">
         <v>674132</v>
@@ -1297,7 +1297,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49555444717407</v>
+        <v>4.49555492401123</v>
       </c>
       <c r="H32" t="n">
         <v>314608</v>
@@ -1442,7 +1442,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>4.73473215103149</v>
+        <v>4.73473167419434</v>
       </c>
       <c r="H37" t="n">
         <v>225190</v>
@@ -1500,7 +1500,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G39" t="n">
-        <v>4.69568252563477</v>
+        <v>4.69568204879761</v>
       </c>
       <c r="H39" t="n">
         <v>178970</v>
@@ -1558,7 +1558,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H41" t="n">
         <v>91478</v>
@@ -1616,7 +1616,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G43" t="n">
-        <v>4.87140464782715</v>
+        <v>4.87140417098999</v>
       </c>
       <c r="H43" t="n">
         <v>182009</v>
@@ -1761,7 +1761,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G48" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H48" t="n">
         <v>115433</v>
@@ -1790,7 +1790,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H49" t="n">
         <v>183086</v>
@@ -1819,7 +1819,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H50" t="n">
         <v>175110</v>
@@ -1935,7 +1935,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>5.14475011825562</v>
+        <v>5.14474964141846</v>
       </c>
       <c r="H54" t="n">
         <v>191951</v>
@@ -2341,7 +2341,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H68" t="n">
         <v>1068513</v>
@@ -2399,7 +2399,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H70" t="n">
         <v>914142</v>
@@ -2428,7 +2428,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H71" t="n">
         <v>493826</v>
@@ -2457,7 +2457,7 @@
         <v>5.875</v>
       </c>
       <c r="G72" t="n">
-        <v>5.73537111282349</v>
+        <v>5.73537063598633</v>
       </c>
       <c r="H72" t="n">
         <v>495492</v>
@@ -2486,7 +2486,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H73" t="n">
         <v>471485</v>
@@ -2573,7 +2573,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81346988677979</v>
+        <v>5.81346940994263</v>
       </c>
       <c r="H76" t="n">
         <v>374070</v>
@@ -2689,7 +2689,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G80" t="n">
-        <v>5.95014238357544</v>
+        <v>5.95014190673828</v>
       </c>
       <c r="H80" t="n">
         <v>281712</v>
@@ -2863,7 +2863,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>6.4236159324646</v>
+        <v>6.42361545562744</v>
       </c>
       <c r="H86" t="n">
         <v>3935460</v>
@@ -2950,7 +2950,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.25765562057495</v>
+        <v>6.25765609741211</v>
       </c>
       <c r="H89" t="n">
         <v>1159466</v>
@@ -3066,7 +3066,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>6.32599210739136</v>
+        <v>6.32599258422852</v>
       </c>
       <c r="H93" t="n">
         <v>305354</v>
@@ -3095,7 +3095,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H94" t="n">
         <v>432458</v>
@@ -3124,7 +3124,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H95" t="n">
         <v>594233</v>
@@ -3240,7 +3240,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G99" t="n">
-        <v>6.41385364532471</v>
+        <v>6.41385316848755</v>
       </c>
       <c r="H99" t="n">
         <v>351799</v>
@@ -3269,7 +3269,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>6.27718067169189</v>
+        <v>6.27718019485474</v>
       </c>
       <c r="H100" t="n">
         <v>191030</v>
@@ -3298,7 +3298,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>6.14050817489624</v>
+        <v>6.14050769805908</v>
       </c>
       <c r="H101" t="n">
         <v>178180</v>
@@ -3530,7 +3530,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>6.00383567810059</v>
+        <v>6.00383520126343</v>
       </c>
       <c r="H109" t="n">
         <v>464426</v>
@@ -3675,7 +3675,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H114" t="n">
         <v>366213</v>
@@ -3704,7 +3704,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>4.85578489303589</v>
+        <v>4.85578441619873</v>
       </c>
       <c r="H115" t="n">
         <v>599949</v>
@@ -3762,7 +3762,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G117" t="n">
-        <v>4.66834831237793</v>
+        <v>4.66834783554077</v>
       </c>
       <c r="H117" t="n">
         <v>385618</v>
@@ -3820,7 +3820,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G119" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H119" t="n">
         <v>641559</v>
@@ -3994,7 +3994,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G125" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H125" t="n">
         <v>252840</v>
@@ -4052,7 +4052,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H127" t="n">
         <v>120276</v>
@@ -4197,7 +4197,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H132" t="n">
         <v>100168</v>
@@ -4255,7 +4255,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H134" t="n">
         <v>236978</v>
@@ -4313,7 +4313,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H136" t="n">
         <v>104225</v>
@@ -4487,7 +4487,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.94462251663208</v>
+        <v>4.94462203979492</v>
       </c>
       <c r="H142" t="n">
         <v>321018</v>
@@ -4632,7 +4632,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G147" t="n">
-        <v>4.63906049728394</v>
+        <v>4.63906097412109</v>
       </c>
       <c r="H147" t="n">
         <v>260005</v>
@@ -4893,7 +4893,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G156" t="n">
-        <v>4.19780397415161</v>
+        <v>4.19780349731445</v>
       </c>
       <c r="H156" t="n">
         <v>212543</v>
@@ -4951,7 +4951,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>3.9830322265625</v>
+        <v>3.98303198814392</v>
       </c>
       <c r="H158" t="n">
         <v>219032</v>
@@ -4980,7 +4980,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G159" t="n">
-        <v>3.94203042984009</v>
+        <v>3.94203019142151</v>
       </c>
       <c r="H159" t="n">
         <v>169167</v>
@@ -5067,7 +5067,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G162" t="n">
-        <v>3.95569777488708</v>
+        <v>3.95569753646851</v>
       </c>
       <c r="H162" t="n">
         <v>1084958</v>
@@ -5125,7 +5125,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G164" t="n">
-        <v>3.98693704605103</v>
+        <v>3.98693752288818</v>
       </c>
       <c r="H164" t="n">
         <v>356103</v>
@@ -5183,7 +5183,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.81707262992859</v>
+        <v>3.81707239151001</v>
       </c>
       <c r="H166" t="n">
         <v>322848</v>
@@ -5241,7 +5241,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G168" t="n">
-        <v>3.79754781723022</v>
+        <v>3.7975480556488</v>
       </c>
       <c r="H168" t="n">
         <v>457065</v>
@@ -5270,7 +5270,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H169" t="n">
         <v>255923</v>
@@ -5328,7 +5328,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G171" t="n">
-        <v>3.81902480125427</v>
+        <v>3.81902503967285</v>
       </c>
       <c r="H171" t="n">
         <v>327719</v>
@@ -5357,7 +5357,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G172" t="n">
-        <v>3.69211483001709</v>
+        <v>3.69211459159851</v>
       </c>
       <c r="H172" t="n">
         <v>305617</v>
@@ -5531,7 +5531,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32505059242249</v>
+        <v>3.32505083084106</v>
       </c>
       <c r="H178" t="n">
         <v>474871</v>
@@ -5560,7 +5560,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>3.34262323379517</v>
+        <v>3.34262299537659</v>
       </c>
       <c r="H179" t="n">
         <v>161143</v>
@@ -5647,7 +5647,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.13761425018311</v>
+        <v>3.13761401176453</v>
       </c>
       <c r="H182" t="n">
         <v>437381</v>
@@ -5792,7 +5792,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G187" t="n">
-        <v>3.18837809562683</v>
+        <v>3.18837833404541</v>
       </c>
       <c r="H187" t="n">
         <v>488386</v>
@@ -5850,7 +5850,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G189" t="n">
-        <v>3.25280976295471</v>
+        <v>3.25280952453613</v>
       </c>
       <c r="H189" t="n">
         <v>273810</v>
@@ -5995,7 +5995,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G194" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H194" t="n">
         <v>420503</v>
@@ -6053,7 +6053,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>3.68039989471436</v>
+        <v>3.68039965629578</v>
       </c>
       <c r="H196" t="n">
         <v>683483</v>
@@ -6140,7 +6140,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G199" t="n">
-        <v>3.56520414352417</v>
+        <v>3.56520438194275</v>
       </c>
       <c r="H199" t="n">
         <v>159477</v>
@@ -6256,7 +6256,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H203" t="n">
         <v>124607</v>
@@ -6285,7 +6285,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H204" t="n">
         <v>425729</v>
@@ -6314,7 +6314,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G205" t="n">
-        <v>3.52225017547607</v>
+        <v>3.5222499370575</v>
       </c>
       <c r="H205" t="n">
         <v>179618</v>
@@ -6401,7 +6401,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G208" t="n">
-        <v>3.50858306884766</v>
+        <v>3.50858283042908</v>
       </c>
       <c r="H208" t="n">
         <v>329671</v>
@@ -6517,7 +6517,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H212" t="n">
         <v>1651359</v>
@@ -6546,7 +6546,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10442233085632</v>
+        <v>3.10442209243774</v>
       </c>
       <c r="H213" t="n">
         <v>298167</v>
@@ -6575,7 +6575,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13175678253174</v>
+        <v>3.13175654411316</v>
       </c>
       <c r="H214" t="n">
         <v>625888</v>
@@ -6720,7 +6720,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G219" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H219" t="n">
         <v>388438</v>
@@ -6778,7 +6778,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H221" t="n">
         <v>298145</v>
@@ -6807,7 +6807,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H222" t="n">
         <v>291818</v>
@@ -6865,7 +6865,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G224" t="n">
-        <v>3.81316757202148</v>
+        <v>3.81316733360291</v>
       </c>
       <c r="H224" t="n">
         <v>314705</v>
@@ -6952,7 +6952,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G227" t="n">
-        <v>3.82878732681274</v>
+        <v>3.82878708839417</v>
       </c>
       <c r="H227" t="n">
         <v>314788</v>
@@ -7155,7 +7155,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G234" t="n">
-        <v>3.42853188514709</v>
+        <v>3.42853164672852</v>
       </c>
       <c r="H234" t="n">
         <v>193610</v>
@@ -7213,7 +7213,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G236" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H236" t="n">
         <v>256484</v>
@@ -7242,7 +7242,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G237" t="n">
-        <v>3.46367621421814</v>
+        <v>3.46367597579956</v>
       </c>
       <c r="H237" t="n">
         <v>248444</v>
@@ -7271,7 +7271,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G238" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H238" t="n">
         <v>586826</v>
@@ -7387,7 +7387,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.18252062797546</v>
+        <v>3.18252086639404</v>
       </c>
       <c r="H242" t="n">
         <v>380348</v>
@@ -7735,7 +7735,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28404903411865</v>
+        <v>3.28404927253723</v>
       </c>
       <c r="H254" t="n">
         <v>798538</v>
@@ -7793,7 +7793,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G256" t="n">
-        <v>3.29381155967712</v>
+        <v>3.29381132125854</v>
       </c>
       <c r="H256" t="n">
         <v>768572</v>
@@ -7880,7 +7880,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G259" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H259" t="n">
         <v>789801</v>
@@ -7996,7 +7996,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>3.25671434402466</v>
+        <v>3.25671458244324</v>
       </c>
       <c r="H263" t="n">
         <v>592087</v>
@@ -8141,7 +8141,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H268" t="n">
         <v>353202</v>
@@ -8199,7 +8199,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G270" t="n">
-        <v>3.37971973419189</v>
+        <v>3.37971997261047</v>
       </c>
       <c r="H270" t="n">
         <v>563976</v>
@@ -8228,7 +8228,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33286094665527</v>
+        <v>3.33286070823669</v>
       </c>
       <c r="H271" t="n">
         <v>548696</v>
@@ -8257,7 +8257,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G272" t="n">
-        <v>3.1766631603241</v>
+        <v>3.17666339874268</v>
       </c>
       <c r="H272" t="n">
         <v>714540</v>
@@ -8344,7 +8344,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G275" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H275" t="n">
         <v>621892</v>
@@ -8518,7 +8518,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G281" t="n">
-        <v>3.52420234680176</v>
+        <v>3.52420258522034</v>
       </c>
       <c r="H281" t="n">
         <v>372312</v>
@@ -8605,7 +8605,7 @@
         <v>3.75</v>
       </c>
       <c r="G284" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H284" t="n">
         <v>746397</v>
@@ -8721,7 +8721,7 @@
         <v>3.75</v>
       </c>
       <c r="G288" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H288" t="n">
         <v>639858</v>
@@ -8779,7 +8779,7 @@
         <v>3.75</v>
       </c>
       <c r="G290" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H290" t="n">
         <v>400304</v>
@@ -8837,7 +8837,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G292" t="n">
-        <v>4.14703941345215</v>
+        <v>4.14703989028931</v>
       </c>
       <c r="H292" t="n">
         <v>1135403</v>
@@ -8895,7 +8895,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G294" t="n">
-        <v>3.93422079086304</v>
+        <v>3.93422055244446</v>
       </c>
       <c r="H294" t="n">
         <v>1490630</v>
@@ -8924,7 +8924,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G295" t="n">
-        <v>3.92055320739746</v>
+        <v>3.92055296897888</v>
       </c>
       <c r="H295" t="n">
         <v>846196</v>
@@ -9011,7 +9011,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>3.76435565948486</v>
+        <v>3.76435589790344</v>
       </c>
       <c r="H298" t="n">
         <v>749553</v>
@@ -9156,7 +9156,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G303" t="n">
-        <v>3.53201246261597</v>
+        <v>3.53201222419739</v>
       </c>
       <c r="H303" t="n">
         <v>279241</v>
@@ -9185,7 +9185,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>3.50272560119629</v>
+        <v>3.50272536277771</v>
       </c>
       <c r="H304" t="n">
         <v>273157</v>
@@ -9214,7 +9214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H305" t="n">
         <v>485224</v>
@@ -9243,7 +9243,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G306" t="n">
-        <v>3.99279475212097</v>
+        <v>3.99279451370239</v>
       </c>
       <c r="H306" t="n">
         <v>1350093</v>
@@ -9446,7 +9446,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G313" t="n">
-        <v>3.96350741386414</v>
+        <v>3.96350765228271</v>
       </c>
       <c r="H313" t="n">
         <v>409216</v>
@@ -9562,7 +9562,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G317" t="n">
-        <v>4.15680170059204</v>
+        <v>4.15680122375488</v>
       </c>
       <c r="H317" t="n">
         <v>455167</v>
@@ -9649,7 +9649,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G320" t="n">
-        <v>4.45357656478882</v>
+        <v>4.45357608795166</v>
       </c>
       <c r="H320" t="n">
         <v>1038374</v>
@@ -27548,6 +27548,35 @@
         <v>141073</v>
       </c>
       <c r="I937" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="s">
+        <v>9</v>
+      </c>
+      <c r="B938" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C938" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D938" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E938" t="n">
+        <v>0.851000010967255</v>
+      </c>
+      <c r="F938" t="n">
+        <v>0.867999970912933</v>
+      </c>
+      <c r="G938" t="n">
+        <v>0.867999970912933</v>
+      </c>
+      <c r="H938" t="n">
+        <v>260101</v>
+      </c>
+      <c r="I938" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -775,7 +775,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H14" t="n">
         <v>670102</v>
@@ -833,7 +833,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H16" t="n">
         <v>231471</v>
@@ -862,7 +862,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H17" t="n">
         <v>158512</v>
@@ -1036,7 +1036,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>5.07641315460205</v>
+        <v>5.07641363143921</v>
       </c>
       <c r="H23" t="n">
         <v>343982</v>
@@ -1065,7 +1065,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G24" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H24" t="n">
         <v>509862</v>
@@ -1123,7 +1123,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>5.02760219573975</v>
+        <v>5.02760171890259</v>
       </c>
       <c r="H26" t="n">
         <v>168190</v>
@@ -1181,7 +1181,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.68592071533203</v>
+        <v>4.68592023849487</v>
       </c>
       <c r="H28" t="n">
         <v>215478</v>
@@ -1210,7 +1210,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89092969894409</v>
+        <v>4.89092922210693</v>
       </c>
       <c r="H29" t="n">
         <v>674132</v>
@@ -1297,7 +1297,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49555492401123</v>
+        <v>4.49555444717407</v>
       </c>
       <c r="H32" t="n">
         <v>314608</v>
@@ -1442,7 +1442,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>4.73473167419434</v>
+        <v>4.73473215103149</v>
       </c>
       <c r="H37" t="n">
         <v>225190</v>
@@ -1500,7 +1500,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G39" t="n">
-        <v>4.69568204879761</v>
+        <v>4.69568252563477</v>
       </c>
       <c r="H39" t="n">
         <v>178970</v>
@@ -1558,7 +1558,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>4.68592071533203</v>
+        <v>4.68592023849487</v>
       </c>
       <c r="H41" t="n">
         <v>91478</v>
@@ -1616,7 +1616,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G43" t="n">
-        <v>4.87140417098999</v>
+        <v>4.87140464782715</v>
       </c>
       <c r="H43" t="n">
         <v>182009</v>
@@ -1761,7 +1761,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G48" t="n">
-        <v>4.86749982833862</v>
+        <v>4.86749935150146</v>
       </c>
       <c r="H48" t="n">
         <v>115433</v>
@@ -1790,7 +1790,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H49" t="n">
         <v>183086</v>
@@ -1819,7 +1819,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>5.02760219573975</v>
+        <v>5.02760171890259</v>
       </c>
       <c r="H50" t="n">
         <v>175110</v>
@@ -1935,7 +1935,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>5.14474964141846</v>
+        <v>5.14475011825562</v>
       </c>
       <c r="H54" t="n">
         <v>191951</v>
@@ -2341,7 +2341,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>5.8378758430481</v>
+        <v>5.83787536621094</v>
       </c>
       <c r="H68" t="n">
         <v>1068513</v>
@@ -2399,7 +2399,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>5.78906345367432</v>
+        <v>5.78906393051147</v>
       </c>
       <c r="H70" t="n">
         <v>914142</v>
@@ -2428,7 +2428,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>5.78906345367432</v>
+        <v>5.78906393051147</v>
       </c>
       <c r="H71" t="n">
         <v>493826</v>
@@ -2457,7 +2457,7 @@
         <v>5.875</v>
       </c>
       <c r="G72" t="n">
-        <v>5.73537063598633</v>
+        <v>5.73537111282349</v>
       </c>
       <c r="H72" t="n">
         <v>495492</v>
@@ -2486,7 +2486,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>5.8378758430481</v>
+        <v>5.83787536621094</v>
       </c>
       <c r="H73" t="n">
         <v>471485</v>
@@ -2573,7 +2573,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81346940994263</v>
+        <v>5.81346988677979</v>
       </c>
       <c r="H76" t="n">
         <v>374070</v>
@@ -2689,7 +2689,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G80" t="n">
-        <v>5.95014190673828</v>
+        <v>5.95014238357544</v>
       </c>
       <c r="H80" t="n">
         <v>281712</v>
@@ -2863,7 +2863,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>6.42361545562744</v>
+        <v>6.4236159324646</v>
       </c>
       <c r="H86" t="n">
         <v>3935460</v>
@@ -2950,7 +2950,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.25765609741211</v>
+        <v>6.25765562057495</v>
       </c>
       <c r="H89" t="n">
         <v>1159466</v>
@@ -3066,7 +3066,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>6.32599258422852</v>
+        <v>6.32599210739136</v>
       </c>
       <c r="H93" t="n">
         <v>305354</v>
@@ -3095,7 +3095,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>6.35039806365967</v>
+        <v>6.35039854049683</v>
       </c>
       <c r="H94" t="n">
         <v>432458</v>
@@ -3124,7 +3124,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.35039806365967</v>
+        <v>6.35039854049683</v>
       </c>
       <c r="H95" t="n">
         <v>594233</v>
@@ -3240,7 +3240,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G99" t="n">
-        <v>6.41385316848755</v>
+        <v>6.41385364532471</v>
       </c>
       <c r="H99" t="n">
         <v>351799</v>
@@ -3269,7 +3269,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>6.27718019485474</v>
+        <v>6.27718067169189</v>
       </c>
       <c r="H100" t="n">
         <v>191030</v>
@@ -3298,7 +3298,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>6.14050769805908</v>
+        <v>6.14050817489624</v>
       </c>
       <c r="H101" t="n">
         <v>178180</v>
@@ -3530,7 +3530,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>6.00383520126343</v>
+        <v>6.00383567810059</v>
       </c>
       <c r="H109" t="n">
         <v>464426</v>
@@ -3675,7 +3675,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H114" t="n">
         <v>366213</v>
@@ -3704,7 +3704,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>4.85578441619873</v>
+        <v>4.85578489303589</v>
       </c>
       <c r="H115" t="n">
         <v>599949</v>
@@ -3762,7 +3762,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G117" t="n">
-        <v>4.66834783554077</v>
+        <v>4.66834831237793</v>
       </c>
       <c r="H117" t="n">
         <v>385618</v>
@@ -3820,7 +3820,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G119" t="n">
-        <v>4.86749982833862</v>
+        <v>4.86749935150146</v>
       </c>
       <c r="H119" t="n">
         <v>641559</v>
@@ -3994,7 +3994,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G125" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H125" t="n">
         <v>252840</v>
@@ -4052,7 +4052,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H127" t="n">
         <v>120276</v>
@@ -4197,7 +4197,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H132" t="n">
         <v>100168</v>
@@ -4255,7 +4255,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H134" t="n">
         <v>236978</v>
@@ -4313,7 +4313,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>5.07641315460205</v>
+        <v>5.07641363143921</v>
       </c>
       <c r="H136" t="n">
         <v>104225</v>
@@ -4487,7 +4487,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.94462203979492</v>
+        <v>4.94462251663208</v>
       </c>
       <c r="H142" t="n">
         <v>321018</v>
@@ -4632,7 +4632,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G147" t="n">
-        <v>4.63906097412109</v>
+        <v>4.63906049728394</v>
       </c>
       <c r="H147" t="n">
         <v>260005</v>
@@ -4893,7 +4893,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G156" t="n">
-        <v>4.19780349731445</v>
+        <v>4.19780397415161</v>
       </c>
       <c r="H156" t="n">
         <v>212543</v>
@@ -4951,7 +4951,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>3.98303198814392</v>
+        <v>3.9830322265625</v>
       </c>
       <c r="H158" t="n">
         <v>219032</v>
@@ -4980,7 +4980,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G159" t="n">
-        <v>3.94203019142151</v>
+        <v>3.94203042984009</v>
       </c>
       <c r="H159" t="n">
         <v>169167</v>
@@ -5067,7 +5067,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G162" t="n">
-        <v>3.95569753646851</v>
+        <v>3.95569777488708</v>
       </c>
       <c r="H162" t="n">
         <v>1084958</v>
@@ -5125,7 +5125,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G164" t="n">
-        <v>3.98693752288818</v>
+        <v>3.98693704605103</v>
       </c>
       <c r="H164" t="n">
         <v>356103</v>
@@ -5183,7 +5183,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.81707239151001</v>
+        <v>3.81707262992859</v>
       </c>
       <c r="H166" t="n">
         <v>322848</v>
@@ -5241,7 +5241,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G168" t="n">
-        <v>3.7975480556488</v>
+        <v>3.79754781723022</v>
       </c>
       <c r="H168" t="n">
         <v>457065</v>
@@ -5270,7 +5270,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73702120780945</v>
+        <v>3.73702144622803</v>
       </c>
       <c r="H169" t="n">
         <v>255923</v>
@@ -5328,7 +5328,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G171" t="n">
-        <v>3.81902503967285</v>
+        <v>3.81902480125427</v>
       </c>
       <c r="H171" t="n">
         <v>327719</v>
@@ -5357,7 +5357,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G172" t="n">
-        <v>3.69211459159851</v>
+        <v>3.69211483001709</v>
       </c>
       <c r="H172" t="n">
         <v>305617</v>
@@ -5531,7 +5531,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32505083084106</v>
+        <v>3.32505059242249</v>
       </c>
       <c r="H178" t="n">
         <v>474871</v>
@@ -5560,7 +5560,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>3.34262299537659</v>
+        <v>3.34262323379517</v>
       </c>
       <c r="H179" t="n">
         <v>161143</v>
@@ -5647,7 +5647,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.13761401176453</v>
+        <v>3.13761425018311</v>
       </c>
       <c r="H182" t="n">
         <v>437381</v>
@@ -5792,7 +5792,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G187" t="n">
-        <v>3.18837833404541</v>
+        <v>3.18837809562683</v>
       </c>
       <c r="H187" t="n">
         <v>488386</v>
@@ -5850,7 +5850,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G189" t="n">
-        <v>3.25280952453613</v>
+        <v>3.25280976295471</v>
       </c>
       <c r="H189" t="n">
         <v>273810</v>
@@ -5995,7 +5995,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G194" t="n">
-        <v>3.24304747581482</v>
+        <v>3.24304723739624</v>
       </c>
       <c r="H194" t="n">
         <v>420503</v>
@@ -6053,7 +6053,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>3.68039965629578</v>
+        <v>3.68039989471436</v>
       </c>
       <c r="H196" t="n">
         <v>683483</v>
@@ -6140,7 +6140,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G199" t="n">
-        <v>3.56520438194275</v>
+        <v>3.56520414352417</v>
       </c>
       <c r="H199" t="n">
         <v>159477</v>
@@ -6256,7 +6256,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59253907203674</v>
+        <v>3.59253883361816</v>
       </c>
       <c r="H203" t="n">
         <v>124607</v>
@@ -6285,7 +6285,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.59253907203674</v>
+        <v>3.59253883361816</v>
       </c>
       <c r="H204" t="n">
         <v>425729</v>
@@ -6314,7 +6314,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G205" t="n">
-        <v>3.5222499370575</v>
+        <v>3.52225017547607</v>
       </c>
       <c r="H205" t="n">
         <v>179618</v>
@@ -6401,7 +6401,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G208" t="n">
-        <v>3.50858283042908</v>
+        <v>3.50858306884766</v>
       </c>
       <c r="H208" t="n">
         <v>329671</v>
@@ -6517,7 +6517,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>3.21571278572083</v>
+        <v>3.21571254730225</v>
       </c>
       <c r="H212" t="n">
         <v>1651359</v>
@@ -6546,7 +6546,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10442209243774</v>
+        <v>3.10442233085632</v>
       </c>
       <c r="H213" t="n">
         <v>298167</v>
@@ -6575,7 +6575,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13175654411316</v>
+        <v>3.13175678253174</v>
       </c>
       <c r="H214" t="n">
         <v>625888</v>
@@ -6720,7 +6720,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G219" t="n">
-        <v>3.4343888759613</v>
+        <v>3.43438911437988</v>
       </c>
       <c r="H219" t="n">
         <v>388438</v>
@@ -6778,7 +6778,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>3.62182593345642</v>
+        <v>3.62182569503784</v>
       </c>
       <c r="H221" t="n">
         <v>298145</v>
@@ -6807,7 +6807,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73702120780945</v>
+        <v>3.73702144622803</v>
       </c>
       <c r="H222" t="n">
         <v>291818</v>
@@ -6865,7 +6865,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G224" t="n">
-        <v>3.81316733360291</v>
+        <v>3.81316757202148</v>
       </c>
       <c r="H224" t="n">
         <v>314705</v>
@@ -6952,7 +6952,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G227" t="n">
-        <v>3.82878708839417</v>
+        <v>3.82878732681274</v>
       </c>
       <c r="H227" t="n">
         <v>314788</v>
@@ -7155,7 +7155,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G234" t="n">
-        <v>3.42853164672852</v>
+        <v>3.42853188514709</v>
       </c>
       <c r="H234" t="n">
         <v>193610</v>
@@ -7213,7 +7213,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G236" t="n">
-        <v>3.4343888759613</v>
+        <v>3.43438911437988</v>
       </c>
       <c r="H236" t="n">
         <v>256484</v>
@@ -7242,7 +7242,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G237" t="n">
-        <v>3.46367597579956</v>
+        <v>3.46367621421814</v>
       </c>
       <c r="H237" t="n">
         <v>248444</v>
@@ -7271,7 +7271,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G238" t="n">
-        <v>3.26647663116455</v>
+        <v>3.26647686958313</v>
       </c>
       <c r="H238" t="n">
         <v>586826</v>
@@ -7387,7 +7387,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.18252086639404</v>
+        <v>3.18252062797546</v>
       </c>
       <c r="H242" t="n">
         <v>380348</v>
@@ -7735,7 +7735,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28404927253723</v>
+        <v>3.28404903411865</v>
       </c>
       <c r="H254" t="n">
         <v>798538</v>
@@ -7793,7 +7793,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G256" t="n">
-        <v>3.29381132125854</v>
+        <v>3.29381155967712</v>
       </c>
       <c r="H256" t="n">
         <v>768572</v>
@@ -7880,7 +7880,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G259" t="n">
-        <v>3.26647663116455</v>
+        <v>3.26647686958313</v>
       </c>
       <c r="H259" t="n">
         <v>789801</v>
@@ -7996,7 +7996,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>3.25671458244324</v>
+        <v>3.25671434402466</v>
       </c>
       <c r="H263" t="n">
         <v>592087</v>
@@ -8141,7 +8141,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>3.24304747581482</v>
+        <v>3.24304723739624</v>
       </c>
       <c r="H268" t="n">
         <v>353202</v>
@@ -8199,7 +8199,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G270" t="n">
-        <v>3.37971997261047</v>
+        <v>3.37971973419189</v>
       </c>
       <c r="H270" t="n">
         <v>563976</v>
@@ -8228,7 +8228,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33286070823669</v>
+        <v>3.33286094665527</v>
       </c>
       <c r="H271" t="n">
         <v>548696</v>
@@ -8257,7 +8257,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G272" t="n">
-        <v>3.17666339874268</v>
+        <v>3.1766631603241</v>
       </c>
       <c r="H272" t="n">
         <v>714540</v>
@@ -8344,7 +8344,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G275" t="n">
-        <v>3.21571278572083</v>
+        <v>3.21571254730225</v>
       </c>
       <c r="H275" t="n">
         <v>621892</v>
@@ -8518,7 +8518,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G281" t="n">
-        <v>3.52420258522034</v>
+        <v>3.52420234680176</v>
       </c>
       <c r="H281" t="n">
         <v>372312</v>
@@ -8605,7 +8605,7 @@
         <v>3.75</v>
       </c>
       <c r="G284" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H284" t="n">
         <v>746397</v>
@@ -8721,7 +8721,7 @@
         <v>3.75</v>
       </c>
       <c r="G288" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H288" t="n">
         <v>639858</v>
@@ -8779,7 +8779,7 @@
         <v>3.75</v>
       </c>
       <c r="G290" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H290" t="n">
         <v>400304</v>
@@ -8837,7 +8837,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G292" t="n">
-        <v>4.14703989028931</v>
+        <v>4.14703941345215</v>
       </c>
       <c r="H292" t="n">
         <v>1135403</v>
@@ -8895,7 +8895,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G294" t="n">
-        <v>3.93422055244446</v>
+        <v>3.93422079086304</v>
       </c>
       <c r="H294" t="n">
         <v>1490630</v>
@@ -8924,7 +8924,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G295" t="n">
-        <v>3.92055296897888</v>
+        <v>3.92055320739746</v>
       </c>
       <c r="H295" t="n">
         <v>846196</v>
@@ -9011,7 +9011,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>3.76435589790344</v>
+        <v>3.76435565948486</v>
       </c>
       <c r="H298" t="n">
         <v>749553</v>
@@ -9156,7 +9156,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G303" t="n">
-        <v>3.53201222419739</v>
+        <v>3.53201246261597</v>
       </c>
       <c r="H303" t="n">
         <v>279241</v>
@@ -9185,7 +9185,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>3.50272536277771</v>
+        <v>3.50272560119629</v>
       </c>
       <c r="H304" t="n">
         <v>273157</v>
@@ -9214,7 +9214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>3.62182593345642</v>
+        <v>3.62182569503784</v>
       </c>
       <c r="H305" t="n">
         <v>485224</v>
@@ -9243,7 +9243,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G306" t="n">
-        <v>3.99279451370239</v>
+        <v>3.99279475212097</v>
       </c>
       <c r="H306" t="n">
         <v>1350093</v>
@@ -9446,7 +9446,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G313" t="n">
-        <v>3.96350765228271</v>
+        <v>3.96350741386414</v>
       </c>
       <c r="H313" t="n">
         <v>409216</v>
@@ -9562,7 +9562,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G317" t="n">
-        <v>4.15680122375488</v>
+        <v>4.15680170059204</v>
       </c>
       <c r="H317" t="n">
         <v>455167</v>
@@ -9649,7 +9649,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G320" t="n">
-        <v>4.45357608795166</v>
+        <v>4.45357656478882</v>
       </c>
       <c r="H320" t="n">
         <v>1038374</v>
@@ -27577,6 +27577,35 @@
         <v>260101</v>
       </c>
       <c r="I938" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="s">
+        <v>9</v>
+      </c>
+      <c r="B939" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C939" t="n">
+        <v>0.865000009536743</v>
+      </c>
+      <c r="D939" t="n">
+        <v>0.878000020980835</v>
+      </c>
+      <c r="E939" t="n">
+        <v>0.832000017166138</v>
+      </c>
+      <c r="F939" t="n">
+        <v>0.840499997138977</v>
+      </c>
+      <c r="G939" t="n">
+        <v>0.840499997138977</v>
+      </c>
+      <c r="H939" t="n">
+        <v>555210</v>
+      </c>
+      <c r="I939" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -775,7 +775,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H14" t="n">
         <v>670102</v>
@@ -833,7 +833,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H16" t="n">
         <v>231471</v>
@@ -862,7 +862,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H17" t="n">
         <v>158512</v>
@@ -1036,7 +1036,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H23" t="n">
         <v>343982</v>
@@ -1065,7 +1065,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G24" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H24" t="n">
         <v>509862</v>
@@ -1123,7 +1123,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H26" t="n">
         <v>168190</v>
@@ -1181,7 +1181,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H28" t="n">
         <v>215478</v>
@@ -1210,7 +1210,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89092922210693</v>
+        <v>4.89092969894409</v>
       </c>
       <c r="H29" t="n">
         <v>674132</v>
@@ -1297,7 +1297,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49555444717407</v>
+        <v>4.49555492401123</v>
       </c>
       <c r="H32" t="n">
         <v>314608</v>
@@ -1442,7 +1442,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>4.73473215103149</v>
+        <v>4.73473167419434</v>
       </c>
       <c r="H37" t="n">
         <v>225190</v>
@@ -1500,7 +1500,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G39" t="n">
-        <v>4.69568252563477</v>
+        <v>4.69568204879761</v>
       </c>
       <c r="H39" t="n">
         <v>178970</v>
@@ -1558,7 +1558,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H41" t="n">
         <v>91478</v>
@@ -1616,7 +1616,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G43" t="n">
-        <v>4.87140464782715</v>
+        <v>4.87140417098999</v>
       </c>
       <c r="H43" t="n">
         <v>182009</v>
@@ -1761,7 +1761,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G48" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H48" t="n">
         <v>115433</v>
@@ -1790,7 +1790,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H49" t="n">
         <v>183086</v>
@@ -1819,7 +1819,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H50" t="n">
         <v>175110</v>
@@ -1935,7 +1935,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>5.14475011825562</v>
+        <v>5.14474964141846</v>
       </c>
       <c r="H54" t="n">
         <v>191951</v>
@@ -2341,7 +2341,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H68" t="n">
         <v>1068513</v>
@@ -2399,7 +2399,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H70" t="n">
         <v>914142</v>
@@ -2428,7 +2428,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H71" t="n">
         <v>493826</v>
@@ -2457,7 +2457,7 @@
         <v>5.875</v>
       </c>
       <c r="G72" t="n">
-        <v>5.73537111282349</v>
+        <v>5.73537063598633</v>
       </c>
       <c r="H72" t="n">
         <v>495492</v>
@@ -2486,7 +2486,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H73" t="n">
         <v>471485</v>
@@ -2573,7 +2573,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81346988677979</v>
+        <v>5.81346940994263</v>
       </c>
       <c r="H76" t="n">
         <v>374070</v>
@@ -2689,7 +2689,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G80" t="n">
-        <v>5.95014238357544</v>
+        <v>5.95014190673828</v>
       </c>
       <c r="H80" t="n">
         <v>281712</v>
@@ -2863,7 +2863,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>6.4236159324646</v>
+        <v>6.42361545562744</v>
       </c>
       <c r="H86" t="n">
         <v>3935460</v>
@@ -2950,7 +2950,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.25765562057495</v>
+        <v>6.25765609741211</v>
       </c>
       <c r="H89" t="n">
         <v>1159466</v>
@@ -3066,7 +3066,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>6.32599210739136</v>
+        <v>6.32599258422852</v>
       </c>
       <c r="H93" t="n">
         <v>305354</v>
@@ -3095,7 +3095,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H94" t="n">
         <v>432458</v>
@@ -3124,7 +3124,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H95" t="n">
         <v>594233</v>
@@ -3240,7 +3240,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G99" t="n">
-        <v>6.41385364532471</v>
+        <v>6.41385316848755</v>
       </c>
       <c r="H99" t="n">
         <v>351799</v>
@@ -3269,7 +3269,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>6.27718067169189</v>
+        <v>6.27718019485474</v>
       </c>
       <c r="H100" t="n">
         <v>191030</v>
@@ -3298,7 +3298,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>6.14050817489624</v>
+        <v>6.14050769805908</v>
       </c>
       <c r="H101" t="n">
         <v>178180</v>
@@ -3530,7 +3530,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>6.00383567810059</v>
+        <v>6.00383520126343</v>
       </c>
       <c r="H109" t="n">
         <v>464426</v>
@@ -3675,7 +3675,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H114" t="n">
         <v>366213</v>
@@ -3704,7 +3704,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>4.85578489303589</v>
+        <v>4.85578441619873</v>
       </c>
       <c r="H115" t="n">
         <v>599949</v>
@@ -3762,7 +3762,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G117" t="n">
-        <v>4.66834831237793</v>
+        <v>4.66834783554077</v>
       </c>
       <c r="H117" t="n">
         <v>385618</v>
@@ -3820,7 +3820,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G119" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H119" t="n">
         <v>641559</v>
@@ -3994,7 +3994,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G125" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H125" t="n">
         <v>252840</v>
@@ -4052,7 +4052,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H127" t="n">
         <v>120276</v>
@@ -4197,7 +4197,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H132" t="n">
         <v>100168</v>
@@ -4255,7 +4255,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H134" t="n">
         <v>236978</v>
@@ -4313,7 +4313,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H136" t="n">
         <v>104225</v>
@@ -4487,7 +4487,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.94462251663208</v>
+        <v>4.94462203979492</v>
       </c>
       <c r="H142" t="n">
         <v>321018</v>
@@ -4632,7 +4632,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G147" t="n">
-        <v>4.63906049728394</v>
+        <v>4.63906097412109</v>
       </c>
       <c r="H147" t="n">
         <v>260005</v>
@@ -4893,7 +4893,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G156" t="n">
-        <v>4.19780397415161</v>
+        <v>4.19780349731445</v>
       </c>
       <c r="H156" t="n">
         <v>212543</v>
@@ -4951,7 +4951,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>3.9830322265625</v>
+        <v>3.98303198814392</v>
       </c>
       <c r="H158" t="n">
         <v>219032</v>
@@ -4980,7 +4980,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G159" t="n">
-        <v>3.94203042984009</v>
+        <v>3.94203019142151</v>
       </c>
       <c r="H159" t="n">
         <v>169167</v>
@@ -5067,7 +5067,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G162" t="n">
-        <v>3.95569777488708</v>
+        <v>3.95569753646851</v>
       </c>
       <c r="H162" t="n">
         <v>1084958</v>
@@ -5125,7 +5125,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G164" t="n">
-        <v>3.98693704605103</v>
+        <v>3.98693752288818</v>
       </c>
       <c r="H164" t="n">
         <v>356103</v>
@@ -5183,7 +5183,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.81707262992859</v>
+        <v>3.81707239151001</v>
       </c>
       <c r="H166" t="n">
         <v>322848</v>
@@ -5241,7 +5241,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G168" t="n">
-        <v>3.79754781723022</v>
+        <v>3.7975480556488</v>
       </c>
       <c r="H168" t="n">
         <v>457065</v>
@@ -5270,7 +5270,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H169" t="n">
         <v>255923</v>
@@ -5328,7 +5328,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G171" t="n">
-        <v>3.81902480125427</v>
+        <v>3.81902503967285</v>
       </c>
       <c r="H171" t="n">
         <v>327719</v>
@@ -5357,7 +5357,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G172" t="n">
-        <v>3.69211483001709</v>
+        <v>3.69211459159851</v>
       </c>
       <c r="H172" t="n">
         <v>305617</v>
@@ -5531,7 +5531,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32505059242249</v>
+        <v>3.32505083084106</v>
       </c>
       <c r="H178" t="n">
         <v>474871</v>
@@ -5560,7 +5560,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>3.34262323379517</v>
+        <v>3.34262299537659</v>
       </c>
       <c r="H179" t="n">
         <v>161143</v>
@@ -5647,7 +5647,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.13761425018311</v>
+        <v>3.13761401176453</v>
       </c>
       <c r="H182" t="n">
         <v>437381</v>
@@ -5792,7 +5792,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G187" t="n">
-        <v>3.18837809562683</v>
+        <v>3.18837833404541</v>
       </c>
       <c r="H187" t="n">
         <v>488386</v>
@@ -5850,7 +5850,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G189" t="n">
-        <v>3.25280976295471</v>
+        <v>3.25280952453613</v>
       </c>
       <c r="H189" t="n">
         <v>273810</v>
@@ -5995,7 +5995,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G194" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H194" t="n">
         <v>420503</v>
@@ -6053,7 +6053,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>3.68039989471436</v>
+        <v>3.68039965629578</v>
       </c>
       <c r="H196" t="n">
         <v>683483</v>
@@ -6140,7 +6140,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G199" t="n">
-        <v>3.56520414352417</v>
+        <v>3.56520438194275</v>
       </c>
       <c r="H199" t="n">
         <v>159477</v>
@@ -6256,7 +6256,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H203" t="n">
         <v>124607</v>
@@ -6285,7 +6285,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H204" t="n">
         <v>425729</v>
@@ -6314,7 +6314,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G205" t="n">
-        <v>3.52225017547607</v>
+        <v>3.5222499370575</v>
       </c>
       <c r="H205" t="n">
         <v>179618</v>
@@ -6401,7 +6401,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G208" t="n">
-        <v>3.50858306884766</v>
+        <v>3.50858283042908</v>
       </c>
       <c r="H208" t="n">
         <v>329671</v>
@@ -6517,7 +6517,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H212" t="n">
         <v>1651359</v>
@@ -6546,7 +6546,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10442233085632</v>
+        <v>3.10442209243774</v>
       </c>
       <c r="H213" t="n">
         <v>298167</v>
@@ -6575,7 +6575,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13175678253174</v>
+        <v>3.13175654411316</v>
       </c>
       <c r="H214" t="n">
         <v>625888</v>
@@ -6720,7 +6720,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G219" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H219" t="n">
         <v>388438</v>
@@ -6778,7 +6778,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H221" t="n">
         <v>298145</v>
@@ -6807,7 +6807,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H222" t="n">
         <v>291818</v>
@@ -6865,7 +6865,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G224" t="n">
-        <v>3.81316757202148</v>
+        <v>3.81316733360291</v>
       </c>
       <c r="H224" t="n">
         <v>314705</v>
@@ -6952,7 +6952,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G227" t="n">
-        <v>3.82878732681274</v>
+        <v>3.82878708839417</v>
       </c>
       <c r="H227" t="n">
         <v>314788</v>
@@ -7155,7 +7155,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G234" t="n">
-        <v>3.42853188514709</v>
+        <v>3.42853164672852</v>
       </c>
       <c r="H234" t="n">
         <v>193610</v>
@@ -7213,7 +7213,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G236" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H236" t="n">
         <v>256484</v>
@@ -7242,7 +7242,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G237" t="n">
-        <v>3.46367621421814</v>
+        <v>3.46367597579956</v>
       </c>
       <c r="H237" t="n">
         <v>248444</v>
@@ -7271,7 +7271,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G238" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H238" t="n">
         <v>586826</v>
@@ -7387,7 +7387,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.18252062797546</v>
+        <v>3.18252086639404</v>
       </c>
       <c r="H242" t="n">
         <v>380348</v>
@@ -7735,7 +7735,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28404903411865</v>
+        <v>3.28404927253723</v>
       </c>
       <c r="H254" t="n">
         <v>798538</v>
@@ -7793,7 +7793,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G256" t="n">
-        <v>3.29381155967712</v>
+        <v>3.29381132125854</v>
       </c>
       <c r="H256" t="n">
         <v>768572</v>
@@ -7880,7 +7880,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G259" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H259" t="n">
         <v>789801</v>
@@ -7996,7 +7996,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>3.25671434402466</v>
+        <v>3.25671458244324</v>
       </c>
       <c r="H263" t="n">
         <v>592087</v>
@@ -8141,7 +8141,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H268" t="n">
         <v>353202</v>
@@ -8199,7 +8199,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G270" t="n">
-        <v>3.37971973419189</v>
+        <v>3.37971997261047</v>
       </c>
       <c r="H270" t="n">
         <v>563976</v>
@@ -8228,7 +8228,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33286094665527</v>
+        <v>3.33286070823669</v>
       </c>
       <c r="H271" t="n">
         <v>548696</v>
@@ -8257,7 +8257,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G272" t="n">
-        <v>3.1766631603241</v>
+        <v>3.17666339874268</v>
       </c>
       <c r="H272" t="n">
         <v>714540</v>
@@ -8344,7 +8344,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G275" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H275" t="n">
         <v>621892</v>
@@ -8518,7 +8518,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G281" t="n">
-        <v>3.52420234680176</v>
+        <v>3.52420258522034</v>
       </c>
       <c r="H281" t="n">
         <v>372312</v>
@@ -8605,7 +8605,7 @@
         <v>3.75</v>
       </c>
       <c r="G284" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H284" t="n">
         <v>746397</v>
@@ -8721,7 +8721,7 @@
         <v>3.75</v>
       </c>
       <c r="G288" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H288" t="n">
         <v>639858</v>
@@ -8779,7 +8779,7 @@
         <v>3.75</v>
       </c>
       <c r="G290" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H290" t="n">
         <v>400304</v>
@@ -8837,7 +8837,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G292" t="n">
-        <v>4.14703941345215</v>
+        <v>4.14703989028931</v>
       </c>
       <c r="H292" t="n">
         <v>1135403</v>
@@ -8895,7 +8895,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G294" t="n">
-        <v>3.93422079086304</v>
+        <v>3.93422055244446</v>
       </c>
       <c r="H294" t="n">
         <v>1490630</v>
@@ -8924,7 +8924,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G295" t="n">
-        <v>3.92055320739746</v>
+        <v>3.92055296897888</v>
       </c>
       <c r="H295" t="n">
         <v>846196</v>
@@ -9011,7 +9011,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>3.76435565948486</v>
+        <v>3.76435589790344</v>
       </c>
       <c r="H298" t="n">
         <v>749553</v>
@@ -9156,7 +9156,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G303" t="n">
-        <v>3.53201246261597</v>
+        <v>3.53201222419739</v>
       </c>
       <c r="H303" t="n">
         <v>279241</v>
@@ -9185,7 +9185,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>3.50272560119629</v>
+        <v>3.50272536277771</v>
       </c>
       <c r="H304" t="n">
         <v>273157</v>
@@ -9214,7 +9214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H305" t="n">
         <v>485224</v>
@@ -9243,7 +9243,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G306" t="n">
-        <v>3.99279475212097</v>
+        <v>3.99279451370239</v>
       </c>
       <c r="H306" t="n">
         <v>1350093</v>
@@ -9446,7 +9446,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G313" t="n">
-        <v>3.96350741386414</v>
+        <v>3.96350765228271</v>
       </c>
       <c r="H313" t="n">
         <v>409216</v>
@@ -9562,7 +9562,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G317" t="n">
-        <v>4.15680170059204</v>
+        <v>4.15680122375488</v>
       </c>
       <c r="H317" t="n">
         <v>455167</v>
@@ -9649,7 +9649,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G320" t="n">
-        <v>4.45357656478882</v>
+        <v>4.45357608795166</v>
       </c>
       <c r="H320" t="n">
         <v>1038374</v>
@@ -27603,9 +27603,38 @@
         <v>0.840499997138977</v>
       </c>
       <c r="H939" t="n">
-        <v>555210</v>
+        <v>568099</v>
       </c>
       <c r="I939" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="s">
+        <v>9</v>
+      </c>
+      <c r="B940" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C940" t="n">
+        <v>0.852500021457672</v>
+      </c>
+      <c r="D940" t="n">
+        <v>0.874499976634979</v>
+      </c>
+      <c r="E940" t="n">
+        <v>0.851000010967255</v>
+      </c>
+      <c r="F940" t="n">
+        <v>0.856000006198883</v>
+      </c>
+      <c r="G940" t="n">
+        <v>0.856000006198883</v>
+      </c>
+      <c r="H940" t="n">
+        <v>184699</v>
+      </c>
+      <c r="I940" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -27638,6 +27638,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" t="s">
+        <v>9</v>
+      </c>
+      <c r="B941" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C941" t="n">
+        <v>0.851999998092651</v>
+      </c>
+      <c r="D941" t="n">
+        <v>0.866999983787537</v>
+      </c>
+      <c r="E941" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="F941" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="G941" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="H941" t="n">
+        <v>138618</v>
+      </c>
+      <c r="I941" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -27667,6 +27667,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="942">
+      <c r="A942" t="s">
+        <v>9</v>
+      </c>
+      <c r="B942" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C942" t="n">
+        <v>0.861500024795532</v>
+      </c>
+      <c r="D942" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="E942" t="n">
+        <v>0.857500016689301</v>
+      </c>
+      <c r="F942" t="n">
+        <v>0.859499990940094</v>
+      </c>
+      <c r="G942" t="n">
+        <v>0.859499990940094</v>
+      </c>
+      <c r="H942" t="n">
+        <v>359941</v>
+      </c>
+      <c r="I942" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -775,7 +775,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H14" t="n">
         <v>670102</v>
@@ -833,7 +833,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H16" t="n">
         <v>231471</v>
@@ -862,7 +862,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>5.41809511184692</v>
+        <v>5.41809558868408</v>
       </c>
       <c r="H17" t="n">
         <v>158512</v>
@@ -1036,7 +1036,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>5.07641315460205</v>
+        <v>5.07641363143921</v>
       </c>
       <c r="H23" t="n">
         <v>343982</v>
@@ -1065,7 +1065,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G24" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H24" t="n">
         <v>509862</v>
@@ -1123,7 +1123,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>5.02760219573975</v>
+        <v>5.02760171890259</v>
       </c>
       <c r="H26" t="n">
         <v>168190</v>
@@ -1181,7 +1181,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.68592071533203</v>
+        <v>4.68592023849487</v>
       </c>
       <c r="H28" t="n">
         <v>215478</v>
@@ -1210,7 +1210,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89092969894409</v>
+        <v>4.89092922210693</v>
       </c>
       <c r="H29" t="n">
         <v>674132</v>
@@ -1297,7 +1297,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49555492401123</v>
+        <v>4.49555444717407</v>
       </c>
       <c r="H32" t="n">
         <v>314608</v>
@@ -1442,7 +1442,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>4.73473167419434</v>
+        <v>4.73473215103149</v>
       </c>
       <c r="H37" t="n">
         <v>225190</v>
@@ -1500,7 +1500,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G39" t="n">
-        <v>4.69568204879761</v>
+        <v>4.69568252563477</v>
       </c>
       <c r="H39" t="n">
         <v>178970</v>
@@ -1558,7 +1558,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>4.68592071533203</v>
+        <v>4.68592023849487</v>
       </c>
       <c r="H41" t="n">
         <v>91478</v>
@@ -1616,7 +1616,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G43" t="n">
-        <v>4.87140417098999</v>
+        <v>4.87140464782715</v>
       </c>
       <c r="H43" t="n">
         <v>182009</v>
@@ -1761,7 +1761,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G48" t="n">
-        <v>4.86749982833862</v>
+        <v>4.86749935150146</v>
       </c>
       <c r="H48" t="n">
         <v>115433</v>
@@ -1790,7 +1790,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H49" t="n">
         <v>183086</v>
@@ -1819,7 +1819,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>5.02760219573975</v>
+        <v>5.02760171890259</v>
       </c>
       <c r="H50" t="n">
         <v>175110</v>
@@ -1935,7 +1935,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>5.14474964141846</v>
+        <v>5.14475011825562</v>
       </c>
       <c r="H54" t="n">
         <v>191951</v>
@@ -2341,7 +2341,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>5.8378758430481</v>
+        <v>5.83787536621094</v>
       </c>
       <c r="H68" t="n">
         <v>1068513</v>
@@ -2399,7 +2399,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>5.78906345367432</v>
+        <v>5.78906393051147</v>
       </c>
       <c r="H70" t="n">
         <v>914142</v>
@@ -2428,7 +2428,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>5.78906345367432</v>
+        <v>5.78906393051147</v>
       </c>
       <c r="H71" t="n">
         <v>493826</v>
@@ -2457,7 +2457,7 @@
         <v>5.875</v>
       </c>
       <c r="G72" t="n">
-        <v>5.73537063598633</v>
+        <v>5.73537111282349</v>
       </c>
       <c r="H72" t="n">
         <v>495492</v>
@@ -2486,7 +2486,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>5.8378758430481</v>
+        <v>5.83787536621094</v>
       </c>
       <c r="H73" t="n">
         <v>471485</v>
@@ -2573,7 +2573,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81346940994263</v>
+        <v>5.81346988677979</v>
       </c>
       <c r="H76" t="n">
         <v>374070</v>
@@ -2689,7 +2689,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G80" t="n">
-        <v>5.95014190673828</v>
+        <v>5.95014238357544</v>
       </c>
       <c r="H80" t="n">
         <v>281712</v>
@@ -2863,7 +2863,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>6.42361545562744</v>
+        <v>6.4236159324646</v>
       </c>
       <c r="H86" t="n">
         <v>3935460</v>
@@ -2950,7 +2950,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.25765609741211</v>
+        <v>6.25765562057495</v>
       </c>
       <c r="H89" t="n">
         <v>1159466</v>
@@ -3066,7 +3066,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>6.32599258422852</v>
+        <v>6.32599210739136</v>
       </c>
       <c r="H93" t="n">
         <v>305354</v>
@@ -3095,7 +3095,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>6.35039806365967</v>
+        <v>6.35039854049683</v>
       </c>
       <c r="H94" t="n">
         <v>432458</v>
@@ -3124,7 +3124,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.35039806365967</v>
+        <v>6.35039854049683</v>
       </c>
       <c r="H95" t="n">
         <v>594233</v>
@@ -3240,7 +3240,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G99" t="n">
-        <v>6.41385316848755</v>
+        <v>6.41385364532471</v>
       </c>
       <c r="H99" t="n">
         <v>351799</v>
@@ -3269,7 +3269,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>6.27718019485474</v>
+        <v>6.27718067169189</v>
       </c>
       <c r="H100" t="n">
         <v>191030</v>
@@ -3298,7 +3298,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>6.14050769805908</v>
+        <v>6.14050817489624</v>
       </c>
       <c r="H101" t="n">
         <v>178180</v>
@@ -3530,7 +3530,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>6.00383520126343</v>
+        <v>6.00383567810059</v>
       </c>
       <c r="H109" t="n">
         <v>464426</v>
@@ -3675,7 +3675,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H114" t="n">
         <v>366213</v>
@@ -3704,7 +3704,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>4.85578441619873</v>
+        <v>4.85578489303589</v>
       </c>
       <c r="H115" t="n">
         <v>599949</v>
@@ -3762,7 +3762,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G117" t="n">
-        <v>4.66834783554077</v>
+        <v>4.66834831237793</v>
       </c>
       <c r="H117" t="n">
         <v>385618</v>
@@ -3820,7 +3820,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G119" t="n">
-        <v>4.86749982833862</v>
+        <v>4.86749935150146</v>
       </c>
       <c r="H119" t="n">
         <v>641559</v>
@@ -3994,7 +3994,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G125" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H125" t="n">
         <v>252840</v>
@@ -4052,7 +4052,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H127" t="n">
         <v>120276</v>
@@ -4197,7 +4197,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>5.23261117935181</v>
+        <v>5.23261070251465</v>
       </c>
       <c r="H132" t="n">
         <v>100168</v>
@@ -4255,7 +4255,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>5.0080771446228</v>
+        <v>5.00807762145996</v>
       </c>
       <c r="H134" t="n">
         <v>236978</v>
@@ -4313,7 +4313,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>5.07641315460205</v>
+        <v>5.07641363143921</v>
       </c>
       <c r="H136" t="n">
         <v>104225</v>
@@ -4487,7 +4487,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.94462203979492</v>
+        <v>4.94462251663208</v>
       </c>
       <c r="H142" t="n">
         <v>321018</v>
@@ -4632,7 +4632,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G147" t="n">
-        <v>4.63906097412109</v>
+        <v>4.63906049728394</v>
       </c>
       <c r="H147" t="n">
         <v>260005</v>
@@ -4893,7 +4893,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G156" t="n">
-        <v>4.19780349731445</v>
+        <v>4.19780397415161</v>
       </c>
       <c r="H156" t="n">
         <v>212543</v>
@@ -4951,7 +4951,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>3.98303198814392</v>
+        <v>3.9830322265625</v>
       </c>
       <c r="H158" t="n">
         <v>219032</v>
@@ -4980,7 +4980,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G159" t="n">
-        <v>3.94203019142151</v>
+        <v>3.94203042984009</v>
       </c>
       <c r="H159" t="n">
         <v>169167</v>
@@ -5067,7 +5067,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G162" t="n">
-        <v>3.95569753646851</v>
+        <v>3.95569777488708</v>
       </c>
       <c r="H162" t="n">
         <v>1084958</v>
@@ -5125,7 +5125,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G164" t="n">
-        <v>3.98693752288818</v>
+        <v>3.98693704605103</v>
       </c>
       <c r="H164" t="n">
         <v>356103</v>
@@ -5183,7 +5183,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.81707239151001</v>
+        <v>3.81707262992859</v>
       </c>
       <c r="H166" t="n">
         <v>322848</v>
@@ -5241,7 +5241,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G168" t="n">
-        <v>3.7975480556488</v>
+        <v>3.79754781723022</v>
       </c>
       <c r="H168" t="n">
         <v>457065</v>
@@ -5270,7 +5270,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73702120780945</v>
+        <v>3.73702144622803</v>
       </c>
       <c r="H169" t="n">
         <v>255923</v>
@@ -5328,7 +5328,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G171" t="n">
-        <v>3.81902503967285</v>
+        <v>3.81902480125427</v>
       </c>
       <c r="H171" t="n">
         <v>327719</v>
@@ -5357,7 +5357,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G172" t="n">
-        <v>3.69211459159851</v>
+        <v>3.69211483001709</v>
       </c>
       <c r="H172" t="n">
         <v>305617</v>
@@ -5531,7 +5531,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32505083084106</v>
+        <v>3.32505059242249</v>
       </c>
       <c r="H178" t="n">
         <v>474871</v>
@@ -5560,7 +5560,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>3.34262299537659</v>
+        <v>3.34262323379517</v>
       </c>
       <c r="H179" t="n">
         <v>161143</v>
@@ -5647,7 +5647,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.13761401176453</v>
+        <v>3.13761425018311</v>
       </c>
       <c r="H182" t="n">
         <v>437381</v>
@@ -5792,7 +5792,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G187" t="n">
-        <v>3.18837833404541</v>
+        <v>3.18837809562683</v>
       </c>
       <c r="H187" t="n">
         <v>488386</v>
@@ -5850,7 +5850,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G189" t="n">
-        <v>3.25280952453613</v>
+        <v>3.25280976295471</v>
       </c>
       <c r="H189" t="n">
         <v>273810</v>
@@ -5995,7 +5995,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G194" t="n">
-        <v>3.24304747581482</v>
+        <v>3.24304723739624</v>
       </c>
       <c r="H194" t="n">
         <v>420503</v>
@@ -6053,7 +6053,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>3.68039965629578</v>
+        <v>3.68039989471436</v>
       </c>
       <c r="H196" t="n">
         <v>683483</v>
@@ -6140,7 +6140,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G199" t="n">
-        <v>3.56520438194275</v>
+        <v>3.56520414352417</v>
       </c>
       <c r="H199" t="n">
         <v>159477</v>
@@ -6256,7 +6256,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59253907203674</v>
+        <v>3.59253883361816</v>
       </c>
       <c r="H203" t="n">
         <v>124607</v>
@@ -6285,7 +6285,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.59253907203674</v>
+        <v>3.59253883361816</v>
       </c>
       <c r="H204" t="n">
         <v>425729</v>
@@ -6314,7 +6314,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G205" t="n">
-        <v>3.5222499370575</v>
+        <v>3.52225017547607</v>
       </c>
       <c r="H205" t="n">
         <v>179618</v>
@@ -6401,7 +6401,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G208" t="n">
-        <v>3.50858283042908</v>
+        <v>3.50858306884766</v>
       </c>
       <c r="H208" t="n">
         <v>329671</v>
@@ -6517,7 +6517,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>3.21571278572083</v>
+        <v>3.21571254730225</v>
       </c>
       <c r="H212" t="n">
         <v>1651359</v>
@@ -6546,7 +6546,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10442209243774</v>
+        <v>3.10442233085632</v>
       </c>
       <c r="H213" t="n">
         <v>298167</v>
@@ -6575,7 +6575,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13175654411316</v>
+        <v>3.13175678253174</v>
       </c>
       <c r="H214" t="n">
         <v>625888</v>
@@ -6720,7 +6720,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G219" t="n">
-        <v>3.4343888759613</v>
+        <v>3.43438911437988</v>
       </c>
       <c r="H219" t="n">
         <v>388438</v>
@@ -6778,7 +6778,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>3.62182593345642</v>
+        <v>3.62182569503784</v>
       </c>
       <c r="H221" t="n">
         <v>298145</v>
@@ -6807,7 +6807,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73702120780945</v>
+        <v>3.73702144622803</v>
       </c>
       <c r="H222" t="n">
         <v>291818</v>
@@ -6865,7 +6865,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G224" t="n">
-        <v>3.81316733360291</v>
+        <v>3.81316757202148</v>
       </c>
       <c r="H224" t="n">
         <v>314705</v>
@@ -6952,7 +6952,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G227" t="n">
-        <v>3.82878708839417</v>
+        <v>3.82878732681274</v>
       </c>
       <c r="H227" t="n">
         <v>314788</v>
@@ -7155,7 +7155,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G234" t="n">
-        <v>3.42853164672852</v>
+        <v>3.42853188514709</v>
       </c>
       <c r="H234" t="n">
         <v>193610</v>
@@ -7213,7 +7213,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G236" t="n">
-        <v>3.4343888759613</v>
+        <v>3.43438911437988</v>
       </c>
       <c r="H236" t="n">
         <v>256484</v>
@@ -7242,7 +7242,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G237" t="n">
-        <v>3.46367597579956</v>
+        <v>3.46367621421814</v>
       </c>
       <c r="H237" t="n">
         <v>248444</v>
@@ -7271,7 +7271,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G238" t="n">
-        <v>3.26647663116455</v>
+        <v>3.26647686958313</v>
       </c>
       <c r="H238" t="n">
         <v>586826</v>
@@ -7387,7 +7387,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.18252086639404</v>
+        <v>3.18252062797546</v>
       </c>
       <c r="H242" t="n">
         <v>380348</v>
@@ -7735,7 +7735,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28404927253723</v>
+        <v>3.28404903411865</v>
       </c>
       <c r="H254" t="n">
         <v>798538</v>
@@ -7793,7 +7793,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G256" t="n">
-        <v>3.29381132125854</v>
+        <v>3.29381155967712</v>
       </c>
       <c r="H256" t="n">
         <v>768572</v>
@@ -7880,7 +7880,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G259" t="n">
-        <v>3.26647663116455</v>
+        <v>3.26647686958313</v>
       </c>
       <c r="H259" t="n">
         <v>789801</v>
@@ -7996,7 +7996,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>3.25671458244324</v>
+        <v>3.25671434402466</v>
       </c>
       <c r="H263" t="n">
         <v>592087</v>
@@ -8141,7 +8141,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>3.24304747581482</v>
+        <v>3.24304723739624</v>
       </c>
       <c r="H268" t="n">
         <v>353202</v>
@@ -8199,7 +8199,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G270" t="n">
-        <v>3.37971997261047</v>
+        <v>3.37971973419189</v>
       </c>
       <c r="H270" t="n">
         <v>563976</v>
@@ -8228,7 +8228,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33286070823669</v>
+        <v>3.33286094665527</v>
       </c>
       <c r="H271" t="n">
         <v>548696</v>
@@ -8257,7 +8257,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G272" t="n">
-        <v>3.17666339874268</v>
+        <v>3.1766631603241</v>
       </c>
       <c r="H272" t="n">
         <v>714540</v>
@@ -8344,7 +8344,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G275" t="n">
-        <v>3.21571278572083</v>
+        <v>3.21571254730225</v>
       </c>
       <c r="H275" t="n">
         <v>621892</v>
@@ -8518,7 +8518,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G281" t="n">
-        <v>3.52420258522034</v>
+        <v>3.52420234680176</v>
       </c>
       <c r="H281" t="n">
         <v>372312</v>
@@ -8605,7 +8605,7 @@
         <v>3.75</v>
       </c>
       <c r="G284" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H284" t="n">
         <v>746397</v>
@@ -8721,7 +8721,7 @@
         <v>3.75</v>
       </c>
       <c r="G288" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H288" t="n">
         <v>639858</v>
@@ -8779,7 +8779,7 @@
         <v>3.75</v>
       </c>
       <c r="G290" t="n">
-        <v>3.66087532043457</v>
+        <v>3.66087508201599</v>
       </c>
       <c r="H290" t="n">
         <v>400304</v>
@@ -8837,7 +8837,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G292" t="n">
-        <v>4.14703989028931</v>
+        <v>4.14703941345215</v>
       </c>
       <c r="H292" t="n">
         <v>1135403</v>
@@ -8895,7 +8895,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G294" t="n">
-        <v>3.93422055244446</v>
+        <v>3.93422079086304</v>
       </c>
       <c r="H294" t="n">
         <v>1490630</v>
@@ -8924,7 +8924,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G295" t="n">
-        <v>3.92055296897888</v>
+        <v>3.92055320739746</v>
       </c>
       <c r="H295" t="n">
         <v>846196</v>
@@ -9011,7 +9011,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>3.76435589790344</v>
+        <v>3.76435565948486</v>
       </c>
       <c r="H298" t="n">
         <v>749553</v>
@@ -9156,7 +9156,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G303" t="n">
-        <v>3.53201222419739</v>
+        <v>3.53201246261597</v>
       </c>
       <c r="H303" t="n">
         <v>279241</v>
@@ -9185,7 +9185,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>3.50272536277771</v>
+        <v>3.50272560119629</v>
       </c>
       <c r="H304" t="n">
         <v>273157</v>
@@ -9214,7 +9214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>3.62182593345642</v>
+        <v>3.62182569503784</v>
       </c>
       <c r="H305" t="n">
         <v>485224</v>
@@ -9243,7 +9243,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G306" t="n">
-        <v>3.99279451370239</v>
+        <v>3.99279475212097</v>
       </c>
       <c r="H306" t="n">
         <v>1350093</v>
@@ -9446,7 +9446,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G313" t="n">
-        <v>3.96350765228271</v>
+        <v>3.96350741386414</v>
       </c>
       <c r="H313" t="n">
         <v>409216</v>
@@ -9562,7 +9562,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G317" t="n">
-        <v>4.15680122375488</v>
+        <v>4.15680170059204</v>
       </c>
       <c r="H317" t="n">
         <v>455167</v>
@@ -9649,7 +9649,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G320" t="n">
-        <v>4.45357608795166</v>
+        <v>4.45357656478882</v>
       </c>
       <c r="H320" t="n">
         <v>1038374</v>
@@ -27693,6 +27693,35 @@
         <v>359941</v>
       </c>
       <c r="I942" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="s">
+        <v>9</v>
+      </c>
+      <c r="B943" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C943" t="n">
+        <v>0.871500015258789</v>
+      </c>
+      <c r="D943" t="n">
+        <v>0.92849999666214</v>
+      </c>
+      <c r="E943" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="F943" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="G943" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="H943" t="n">
+        <v>570069</v>
+      </c>
+      <c r="I943" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EGLA.MI.xlsx
+++ b/data/EGLA.MI.xlsx
@@ -775,7 +775,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H14" t="n">
         <v>670102</v>
@@ -833,7 +833,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H16" t="n">
         <v>231471</v>
@@ -862,7 +862,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>5.41809558868408</v>
+        <v>5.41809511184692</v>
       </c>
       <c r="H17" t="n">
         <v>158512</v>
@@ -1036,7 +1036,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G23" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H23" t="n">
         <v>343982</v>
@@ -1065,7 +1065,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G24" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H24" t="n">
         <v>509862</v>
@@ -1123,7 +1123,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H26" t="n">
         <v>168190</v>
@@ -1181,7 +1181,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H28" t="n">
         <v>215478</v>
@@ -1210,7 +1210,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.89092922210693</v>
+        <v>4.89092969894409</v>
       </c>
       <c r="H29" t="n">
         <v>674132</v>
@@ -1297,7 +1297,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49555444717407</v>
+        <v>4.49555492401123</v>
       </c>
       <c r="H32" t="n">
         <v>314608</v>
@@ -1442,7 +1442,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>4.73473215103149</v>
+        <v>4.73473167419434</v>
       </c>
       <c r="H37" t="n">
         <v>225190</v>
@@ -1500,7 +1500,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G39" t="n">
-        <v>4.69568252563477</v>
+        <v>4.69568204879761</v>
       </c>
       <c r="H39" t="n">
         <v>178970</v>
@@ -1558,7 +1558,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>4.68592023849487</v>
+        <v>4.68592071533203</v>
       </c>
       <c r="H41" t="n">
         <v>91478</v>
@@ -1616,7 +1616,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G43" t="n">
-        <v>4.87140464782715</v>
+        <v>4.87140417098999</v>
       </c>
       <c r="H43" t="n">
         <v>182009</v>
@@ -1761,7 +1761,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G48" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H48" t="n">
         <v>115433</v>
@@ -1790,7 +1790,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H49" t="n">
         <v>183086</v>
@@ -1819,7 +1819,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>5.02760171890259</v>
+        <v>5.02760219573975</v>
       </c>
       <c r="H50" t="n">
         <v>175110</v>
@@ -1935,7 +1935,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>5.14475011825562</v>
+        <v>5.14474964141846</v>
       </c>
       <c r="H54" t="n">
         <v>191951</v>
@@ -2341,7 +2341,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H68" t="n">
         <v>1068513</v>
@@ -2399,7 +2399,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H70" t="n">
         <v>914142</v>
@@ -2428,7 +2428,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>5.78906393051147</v>
+        <v>5.78906345367432</v>
       </c>
       <c r="H71" t="n">
         <v>493826</v>
@@ -2457,7 +2457,7 @@
         <v>5.875</v>
       </c>
       <c r="G72" t="n">
-        <v>5.73537111282349</v>
+        <v>5.73537063598633</v>
       </c>
       <c r="H72" t="n">
         <v>495492</v>
@@ -2486,7 +2486,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>5.83787536621094</v>
+        <v>5.8378758430481</v>
       </c>
       <c r="H73" t="n">
         <v>471485</v>
@@ -2573,7 +2573,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81346988677979</v>
+        <v>5.81346940994263</v>
       </c>
       <c r="H76" t="n">
         <v>374070</v>
@@ -2689,7 +2689,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G80" t="n">
-        <v>5.95014238357544</v>
+        <v>5.95014190673828</v>
       </c>
       <c r="H80" t="n">
         <v>281712</v>
@@ -2863,7 +2863,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>6.4236159324646</v>
+        <v>6.42361545562744</v>
       </c>
       <c r="H86" t="n">
         <v>3935460</v>
@@ -2950,7 +2950,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.25765562057495</v>
+        <v>6.25765609741211</v>
       </c>
       <c r="H89" t="n">
         <v>1159466</v>
@@ -3066,7 +3066,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>6.32599210739136</v>
+        <v>6.32599258422852</v>
       </c>
       <c r="H93" t="n">
         <v>305354</v>
@@ -3095,7 +3095,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H94" t="n">
         <v>432458</v>
@@ -3124,7 +3124,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.35039854049683</v>
+        <v>6.35039806365967</v>
       </c>
       <c r="H95" t="n">
         <v>594233</v>
@@ -3240,7 +3240,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G99" t="n">
-        <v>6.41385364532471</v>
+        <v>6.41385316848755</v>
       </c>
       <c r="H99" t="n">
         <v>351799</v>
@@ -3269,7 +3269,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>6.27718067169189</v>
+        <v>6.27718019485474</v>
       </c>
       <c r="H100" t="n">
         <v>191030</v>
@@ -3298,7 +3298,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>6.14050817489624</v>
+        <v>6.14050769805908</v>
       </c>
       <c r="H101" t="n">
         <v>178180</v>
@@ -3530,7 +3530,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>6.00383567810059</v>
+        <v>6.00383520126343</v>
       </c>
       <c r="H109" t="n">
         <v>464426</v>
@@ -3675,7 +3675,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H114" t="n">
         <v>366213</v>
@@ -3704,7 +3704,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>4.85578489303589</v>
+        <v>4.85578441619873</v>
       </c>
       <c r="H115" t="n">
         <v>599949</v>
@@ -3762,7 +3762,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G117" t="n">
-        <v>4.66834831237793</v>
+        <v>4.66834783554077</v>
       </c>
       <c r="H117" t="n">
         <v>385618</v>
@@ -3820,7 +3820,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G119" t="n">
-        <v>4.86749935150146</v>
+        <v>4.86749982833862</v>
       </c>
       <c r="H119" t="n">
         <v>641559</v>
@@ -3994,7 +3994,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G125" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H125" t="n">
         <v>252840</v>
@@ -4052,7 +4052,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H127" t="n">
         <v>120276</v>
@@ -4197,7 +4197,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>5.23261070251465</v>
+        <v>5.23261117935181</v>
       </c>
       <c r="H132" t="n">
         <v>100168</v>
@@ -4255,7 +4255,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>5.00807762145996</v>
+        <v>5.0080771446228</v>
       </c>
       <c r="H134" t="n">
         <v>236978</v>
@@ -4313,7 +4313,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>5.07641363143921</v>
+        <v>5.07641315460205</v>
       </c>
       <c r="H136" t="n">
         <v>104225</v>
@@ -4487,7 +4487,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>4.94462251663208</v>
+        <v>4.94462203979492</v>
       </c>
       <c r="H142" t="n">
         <v>321018</v>
@@ -4632,7 +4632,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G147" t="n">
-        <v>4.63906049728394</v>
+        <v>4.63906097412109</v>
       </c>
       <c r="H147" t="n">
         <v>260005</v>
@@ -4893,7 +4893,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G156" t="n">
-        <v>4.19780397415161</v>
+        <v>4.19780349731445</v>
       </c>
       <c r="H156" t="n">
         <v>212543</v>
@@ -4951,7 +4951,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>3.9830322265625</v>
+        <v>3.98303198814392</v>
       </c>
       <c r="H158" t="n">
         <v>219032</v>
@@ -4980,7 +4980,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G159" t="n">
-        <v>3.94203042984009</v>
+        <v>3.94203019142151</v>
       </c>
       <c r="H159" t="n">
         <v>169167</v>
@@ -5067,7 +5067,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G162" t="n">
-        <v>3.95569777488708</v>
+        <v>3.95569753646851</v>
       </c>
       <c r="H162" t="n">
         <v>1084958</v>
@@ -5125,7 +5125,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G164" t="n">
-        <v>3.98693704605103</v>
+        <v>3.98693752288818</v>
       </c>
       <c r="H164" t="n">
         <v>356103</v>
@@ -5183,7 +5183,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.81707262992859</v>
+        <v>3.81707239151001</v>
       </c>
       <c r="H166" t="n">
         <v>322848</v>
@@ -5241,7 +5241,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G168" t="n">
-        <v>3.79754781723022</v>
+        <v>3.7975480556488</v>
       </c>
       <c r="H168" t="n">
         <v>457065</v>
@@ -5270,7 +5270,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H169" t="n">
         <v>255923</v>
@@ -5328,7 +5328,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G171" t="n">
-        <v>3.81902480125427</v>
+        <v>3.81902503967285</v>
       </c>
       <c r="H171" t="n">
         <v>327719</v>
@@ -5357,7 +5357,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G172" t="n">
-        <v>3.69211483001709</v>
+        <v>3.69211459159851</v>
       </c>
       <c r="H172" t="n">
         <v>305617</v>
@@ -5531,7 +5531,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32505059242249</v>
+        <v>3.32505083084106</v>
       </c>
       <c r="H178" t="n">
         <v>474871</v>
@@ -5560,7 +5560,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>3.34262323379517</v>
+        <v>3.34262299537659</v>
       </c>
       <c r="H179" t="n">
         <v>161143</v>
@@ -5647,7 +5647,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.13761425018311</v>
+        <v>3.13761401176453</v>
       </c>
       <c r="H182" t="n">
         <v>437381</v>
@@ -5792,7 +5792,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G187" t="n">
-        <v>3.18837809562683</v>
+        <v>3.18837833404541</v>
       </c>
       <c r="H187" t="n">
         <v>488386</v>
@@ -5850,7 +5850,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G189" t="n">
-        <v>3.25280976295471</v>
+        <v>3.25280952453613</v>
       </c>
       <c r="H189" t="n">
         <v>273810</v>
@@ -5995,7 +5995,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G194" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H194" t="n">
         <v>420503</v>
@@ -6053,7 +6053,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>3.68039989471436</v>
+        <v>3.68039965629578</v>
       </c>
       <c r="H196" t="n">
         <v>683483</v>
@@ -6140,7 +6140,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G199" t="n">
-        <v>3.56520414352417</v>
+        <v>3.56520438194275</v>
       </c>
       <c r="H199" t="n">
         <v>159477</v>
@@ -6256,7 +6256,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H203" t="n">
         <v>124607</v>
@@ -6285,7 +6285,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.59253883361816</v>
+        <v>3.59253907203674</v>
       </c>
       <c r="H204" t="n">
         <v>425729</v>
@@ -6314,7 +6314,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G205" t="n">
-        <v>3.52225017547607</v>
+        <v>3.5222499370575</v>
       </c>
       <c r="H205" t="n">
         <v>179618</v>
@@ -6401,7 +6401,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G208" t="n">
-        <v>3.50858306884766</v>
+        <v>3.50858283042908</v>
       </c>
       <c r="H208" t="n">
         <v>329671</v>
@@ -6517,7 +6517,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H212" t="n">
         <v>1651359</v>
@@ -6546,7 +6546,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10442233085632</v>
+        <v>3.10442209243774</v>
       </c>
       <c r="H213" t="n">
         <v>298167</v>
@@ -6575,7 +6575,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13175678253174</v>
+        <v>3.13175654411316</v>
       </c>
       <c r="H214" t="n">
         <v>625888</v>
@@ -6720,7 +6720,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G219" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H219" t="n">
         <v>388438</v>
@@ -6778,7 +6778,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H221" t="n">
         <v>298145</v>
@@ -6807,7 +6807,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73702144622803</v>
+        <v>3.73702120780945</v>
       </c>
       <c r="H222" t="n">
         <v>291818</v>
@@ -6865,7 +6865,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G224" t="n">
-        <v>3.81316757202148</v>
+        <v>3.81316733360291</v>
       </c>
       <c r="H224" t="n">
         <v>314705</v>
@@ -6952,7 +6952,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G227" t="n">
-        <v>3.82878732681274</v>
+        <v>3.82878708839417</v>
       </c>
       <c r="H227" t="n">
         <v>314788</v>
@@ -7155,7 +7155,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G234" t="n">
-        <v>3.42853188514709</v>
+        <v>3.42853164672852</v>
       </c>
       <c r="H234" t="n">
         <v>193610</v>
@@ -7213,7 +7213,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G236" t="n">
-        <v>3.43438911437988</v>
+        <v>3.4343888759613</v>
       </c>
       <c r="H236" t="n">
         <v>256484</v>
@@ -7242,7 +7242,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G237" t="n">
-        <v>3.46367621421814</v>
+        <v>3.46367597579956</v>
       </c>
       <c r="H237" t="n">
         <v>248444</v>
@@ -7271,7 +7271,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G238" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H238" t="n">
         <v>586826</v>
@@ -7387,7 +7387,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.18252062797546</v>
+        <v>3.18252086639404</v>
       </c>
       <c r="H242" t="n">
         <v>380348</v>
@@ -7735,7 +7735,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28404903411865</v>
+        <v>3.28404927253723</v>
       </c>
       <c r="H254" t="n">
         <v>798538</v>
@@ -7793,7 +7793,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G256" t="n">
-        <v>3.29381155967712</v>
+        <v>3.29381132125854</v>
       </c>
       <c r="H256" t="n">
         <v>768572</v>
@@ -7880,7 +7880,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G259" t="n">
-        <v>3.26647686958313</v>
+        <v>3.26647663116455</v>
       </c>
       <c r="H259" t="n">
         <v>789801</v>
@@ -7996,7 +7996,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>3.25671434402466</v>
+        <v>3.25671458244324</v>
       </c>
       <c r="H263" t="n">
         <v>592087</v>
@@ -8141,7 +8141,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>3.24304723739624</v>
+        <v>3.24304747581482</v>
       </c>
       <c r="H268" t="n">
         <v>353202</v>
@@ -8199,7 +8199,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G270" t="n">
-        <v>3.37971973419189</v>
+        <v>3.37971997261047</v>
       </c>
       <c r="H270" t="n">
         <v>563976</v>
@@ -8228,7 +8228,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33286094665527</v>
+        <v>3.33286070823669</v>
       </c>
       <c r="H271" t="n">
         <v>548696</v>
@@ -8257,7 +8257,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G272" t="n">
-        <v>3.1766631603241</v>
+        <v>3.17666339874268</v>
       </c>
       <c r="H272" t="n">
         <v>714540</v>
@@ -8344,7 +8344,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G275" t="n">
-        <v>3.21571254730225</v>
+        <v>3.21571278572083</v>
       </c>
       <c r="H275" t="n">
         <v>621892</v>
@@ -8518,7 +8518,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G281" t="n">
-        <v>3.52420234680176</v>
+        <v>3.52420258522034</v>
       </c>
       <c r="H281" t="n">
         <v>372312</v>
@@ -8605,7 +8605,7 @@
         <v>3.75</v>
       </c>
       <c r="G284" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H284" t="n">
         <v>746397</v>
@@ -8721,7 +8721,7 @@
         <v>3.75</v>
       </c>
       <c r="G288" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H288" t="n">
         <v>639858</v>
@@ -8779,7 +8779,7 @@
         <v>3.75</v>
       </c>
       <c r="G290" t="n">
-        <v>3.66087508201599</v>
+        <v>3.66087532043457</v>
       </c>
       <c r="H290" t="n">
         <v>400304</v>
@@ -8837,7 +8837,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G292" t="n">
-        <v>4.14703941345215</v>
+        <v>4.14703989028931</v>
       </c>
       <c r="H292" t="n">
         <v>1135403</v>
@@ -8895,7 +8895,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G294" t="n">
-        <v>3.93422079086304</v>
+        <v>3.93422055244446</v>
       </c>
       <c r="H294" t="n">
         <v>1490630</v>
@@ -8924,7 +8924,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G295" t="n">
-        <v>3.92055320739746</v>
+        <v>3.92055296897888</v>
       </c>
       <c r="H295" t="n">
         <v>846196</v>
@@ -9011,7 +9011,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>3.76435565948486</v>
+        <v>3.76435589790344</v>
       </c>
       <c r="H298" t="n">
         <v>749553</v>
@@ -9156,7 +9156,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G303" t="n">
-        <v>3.53201246261597</v>
+        <v>3.53201222419739</v>
       </c>
       <c r="H303" t="n">
         <v>279241</v>
@@ -9185,7 +9185,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>3.50272560119629</v>
+        <v>3.50272536277771</v>
       </c>
       <c r="H304" t="n">
         <v>273157</v>
@@ -9214,7 +9214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>3.62182569503784</v>
+        <v>3.62182593345642</v>
       </c>
       <c r="H305" t="n">
         <v>485224</v>
@@ -9243,7 +9243,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G306" t="n">
-        <v>3.99279475212097</v>
+        <v>3.99279451370239</v>
       </c>
       <c r="H306" t="n">
         <v>1350093</v>
@@ -9446,7 +9446,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G313" t="n">
-        <v>3.96350741386414</v>
+        <v>3.96350765228271</v>
       </c>
       <c r="H313" t="n">
         <v>409216</v>
@@ -9562,7 +9562,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G317" t="n">
-        <v>4.15680170059204</v>
+        <v>4.15680122375488</v>
       </c>
       <c r="H317" t="n">
         <v>455167</v>
@@ -9649,7 +9649,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G320" t="n">
-        <v>4.45357656478882</v>
+        <v>4.45357608795166</v>
       </c>
       <c r="H320" t="n">
         <v>1038374</v>
@@ -27719,9 +27719,38 @@
         <v>0.910000026226044</v>
       </c>
       <c r="H943" t="n">
-        <v>570069</v>
+        <v>571870</v>
       </c>
       <c r="I943" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="s">
+        <v>9</v>
+      </c>
+      <c r="B944" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C944" t="n">
+        <v>0.897000014781952</v>
+      </c>
+      <c r="D944" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="E944" t="n">
+        <v>0.869499981403351</v>
+      </c>
+      <c r="F944" t="n">
+        <v>0.875500023365021</v>
+      </c>
+      <c r="G944" t="n">
+        <v>0.875500023365021</v>
+      </c>
+      <c r="H944" t="n">
+        <v>355757</v>
+      </c>
+      <c r="I944" t="s">
         <v>9</v>
       </c>
     </row>
